--- a/news_daily/2026-09-08.xlsx
+++ b/news_daily/2026-09-08.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BH$22</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BH$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BH$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BH$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -89,10 +89,10 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH22"/>
+  <dimension ref="A1:BL22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -526,6 +526,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -829,6 +833,26 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -864,28 +888,32 @@
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>重大訴訟</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -925,7 +953,7 @@
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>MAJOR_LITIGATION</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -934,7 +962,11 @@
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr"/>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>e25a32a08e7c4112a3b890b97349f78b</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>38689a87aedbe85511549073</t>
@@ -955,7 +987,11 @@
       <c r="AL2" s="2" t="inlineStr"/>
       <c r="AM2" s="2" t="inlineStr"/>
       <c r="AN2" s="2" t="inlineStr"/>
-      <c r="AO2" s="2" t="inlineStr"/>
+      <c r="AO2" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP2" s="2" t="inlineStr"/>
       <c r="AQ2" s="2" t="inlineStr"/>
       <c r="AR2" s="2" t="inlineStr"/>
@@ -991,516 +1027,584 @@
         </is>
       </c>
       <c r="BH2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>GDDY</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>GoDaddy Inc. Class A Common Stock</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>2026-09-08T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>GoDaddy Shares Fall as Downgrade Fallout and Lawsuit Overhang Pressure Sentiment</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>分析師降評</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr"/>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>'-0.956</t>
         </is>
       </c>
-      <c r="P3" s="3" t="inlineStr"/>
-      <c r="Q3" s="3" t="inlineStr"/>
-      <c r="R3" s="3" t="inlineStr"/>
-      <c r="S3" s="3" t="inlineStr"/>
-      <c r="T3" s="3" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr"/>
+      <c r="Q3" s="2" t="inlineStr"/>
+      <c r="R3" s="2" t="inlineStr"/>
+      <c r="S3" s="2" t="inlineStr"/>
+      <c r="T3" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U3" s="3" t="inlineStr">
+      <c r="U3" s="2" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPeFctSUxubGtnQVFlNW81LXRBWmJCME43LTFSMGVNOTAzNUhqYmppcGVLMHpDZ2RtRjdSVy1xTE5VaENsUGstSGY1NXF2eGpmOXE4akhCaWhfcnkycndicTZieWpDTHgwZDgzNEtBbWlIV0ZhZFZoM0FkMjJVQmJQQmxYUjdHTDZlX3VnZTgzaWUzVmNXeVVPQm9WNld0RmlrYVlnYUtGMnIxV3JjbnFUQmE3Yw?oc=5</t>
         </is>
       </c>
-      <c r="V3" s="3" t="inlineStr">
+      <c r="V3" s="2" t="inlineStr">
         <is>
           <t>Quiver Quantitative</t>
         </is>
       </c>
-      <c r="W3" s="3" t="inlineStr"/>
-      <c r="X3" s="3" t="inlineStr">
+      <c r="W3" s="2" t="inlineStr"/>
+      <c r="X3" s="2" t="inlineStr">
         <is>
           <t>MARKET</t>
         </is>
       </c>
-      <c r="Y3" s="3" t="inlineStr">
+      <c r="Y3" s="2" t="inlineStr">
         <is>
           <t>ANALYST_DOWNGRADE</t>
         </is>
       </c>
-      <c r="Z3" s="3" t="inlineStr">
+      <c r="Z3" s="2" t="inlineStr">
         <is>
           <t>downgrade</t>
         </is>
       </c>
-      <c r="AA3" s="3" t="inlineStr"/>
-      <c r="AB3" s="3" t="inlineStr"/>
-      <c r="AC3" s="3" t="inlineStr">
+      <c r="AA3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AC3" s="2" t="inlineStr">
         <is>
           <t>c21718b1c0dcb59110dc7a07</t>
         </is>
       </c>
-      <c r="AD3" s="3" t="inlineStr">
+      <c r="AD3" s="2" t="inlineStr">
         <is>
           <t>d35b1b687fbf346773c68937</t>
         </is>
       </c>
-      <c r="AE3" s="3" t="inlineStr"/>
-      <c r="AF3" s="3" t="inlineStr"/>
-      <c r="AG3" s="3" t="inlineStr"/>
-      <c r="AH3" s="3" t="inlineStr"/>
-      <c r="AI3" s="3" t="inlineStr"/>
-      <c r="AJ3" s="3" t="inlineStr"/>
-      <c r="AK3" s="3" t="inlineStr"/>
-      <c r="AL3" s="3" t="inlineStr"/>
-      <c r="AM3" s="3" t="inlineStr"/>
-      <c r="AN3" s="3" t="inlineStr"/>
-      <c r="AO3" s="3" t="inlineStr"/>
-      <c r="AP3" s="3" t="inlineStr"/>
-      <c r="AQ3" s="3" t="inlineStr"/>
-      <c r="AR3" s="3" t="inlineStr"/>
-      <c r="AS3" s="3" t="inlineStr"/>
-      <c r="AT3" s="3" t="inlineStr"/>
-      <c r="AU3" s="3" t="inlineStr"/>
-      <c r="AV3" s="3" t="inlineStr"/>
-      <c r="AW3" s="3" t="inlineStr">
+      <c r="AE3" s="2" t="inlineStr"/>
+      <c r="AF3" s="2" t="inlineStr"/>
+      <c r="AG3" s="2" t="inlineStr"/>
+      <c r="AH3" s="2" t="inlineStr"/>
+      <c r="AI3" s="2" t="inlineStr"/>
+      <c r="AJ3" s="2" t="inlineStr"/>
+      <c r="AK3" s="2" t="inlineStr"/>
+      <c r="AL3" s="2" t="inlineStr"/>
+      <c r="AM3" s="2" t="inlineStr"/>
+      <c r="AN3" s="2" t="inlineStr"/>
+      <c r="AO3" s="2" t="inlineStr"/>
+      <c r="AP3" s="2" t="inlineStr"/>
+      <c r="AQ3" s="2" t="inlineStr"/>
+      <c r="AR3" s="2" t="inlineStr"/>
+      <c r="AS3" s="2" t="inlineStr"/>
+      <c r="AT3" s="2" t="inlineStr"/>
+      <c r="AU3" s="2" t="inlineStr"/>
+      <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" s="2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX3" s="3" t="inlineStr"/>
-      <c r="AY3" s="3" t="inlineStr"/>
-      <c r="AZ3" s="3" t="inlineStr"/>
-      <c r="BA3" s="3" t="inlineStr"/>
-      <c r="BB3" s="3" t="inlineStr">
+      <c r="AX3" s="2" t="inlineStr"/>
+      <c r="AY3" s="2" t="inlineStr"/>
+      <c r="AZ3" s="2" t="inlineStr"/>
+      <c r="BA3" s="2" t="inlineStr"/>
+      <c r="BB3" s="2" t="inlineStr">
         <is>
           <t>GDDY</t>
         </is>
       </c>
-      <c r="BC3" s="3" t="inlineStr">
+      <c r="BC3" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD3" s="3" t="inlineStr"/>
-      <c r="BE3" s="3" t="inlineStr">
+      <c r="BD3" s="2" t="inlineStr"/>
+      <c r="BE3" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF3" s="3" t="inlineStr">
+      <c r="BF3" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG3" s="3" t="inlineStr">
+      <c r="BG3" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH3" s="3" t="inlineStr"/>
+      <c r="BH3" s="2" t="inlineStr"/>
+      <c r="BI3" s="2" t="inlineStr"/>
+      <c r="BJ3" s="2" t="inlineStr"/>
+      <c r="BK3" s="2" t="inlineStr"/>
+      <c r="BL3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>COR</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Cencora, Inc. Common Stock</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>2026-09-08T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Cencora's MWI Animal Health Merger With Covetrus Sees 'Intensified' FTC Scrutiny, RBC Says</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>監管調查</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、持續追蹤</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>'-0.836</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr"/>
+      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="R4" s="3" t="inlineStr"/>
+      <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxQYks2S2xRUDV1SDNjTVVLNFIxR1JFeGp4NHpqekh2bV83cHhNcXFtVDhja2Y3UTgzeTczNk9wZ2dlTlFoRlZEQjNLWElWZ0hsTERPck1kNm1zaG9BTG1YRVpqaU9QODZTb3RCNTdKMVJmYWR0U0Ric3lKV0NaMENiUVRBb0djZTkxYkRPMnNXaktPTm9YbmItZG9qTHgyS0thdzN2VnFrUTFkYlZaOVdKZDU3LVNsOElkRmZxVW9EWFRhNHYyaWVxbjhsbm12TWdINHV1akpKRQ?oc=5</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>marketscreener.com</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr"/>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr">
+        <is>
+          <t>REGULATORY_INVESTIGATION</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>FTC</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr"/>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>44404b955f634b7ba8b076c5a6547b22</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>db5f8074242257836e38369f</t>
+        </is>
+      </c>
+      <c r="AD4" s="3" t="inlineStr">
+        <is>
+          <t>5f519eb5972478e4621689ff</t>
+        </is>
+      </c>
+      <c r="AE4" s="3" t="inlineStr"/>
+      <c r="AF4" s="3" t="inlineStr"/>
+      <c r="AG4" s="3" t="inlineStr"/>
+      <c r="AH4" s="3" t="inlineStr"/>
+      <c r="AI4" s="3" t="inlineStr"/>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" s="3" t="inlineStr"/>
+      <c r="AM4" s="3" t="inlineStr"/>
+      <c r="AN4" s="3" t="inlineStr"/>
+      <c r="AO4" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>'-0.836</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr"/>
-      <c r="Q4" s="2" t="inlineStr"/>
-      <c r="R4" s="2" t="inlineStr"/>
-      <c r="S4" s="2" t="inlineStr"/>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxQYks2S2xRUDV1SDNjTVVLNFIxR1JFeGp4NHpqekh2bV83cHhNcXFtVDhja2Y3UTgzeTczNk9wZ2dlTlFoRlZEQjNLWElWZ0hsTERPck1kNm1zaG9BTG1YRVpqaU9QODZTb3RCNTdKMVJmYWR0U0Ric3lKV0NaMENiUVRBb0djZTkxYkRPMnNXaktPTm9YbmItZG9qTHgyS0thdzN2VnFrUTFkYlZaOVdKZDU3LVNsOElkRmZxVW9EWFRhNHYyaWVxbjhsbm12TWdINHV1akpKRQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>marketscreener.com</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr"/>
-      <c r="X4" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y4" s="2" t="inlineStr">
-        <is>
-          <t>REGULATORY_INVESTIGATION</t>
-        </is>
-      </c>
-      <c r="Z4" s="2" t="inlineStr">
-        <is>
-          <t>FTC</t>
-        </is>
-      </c>
-      <c r="AA4" s="2" t="inlineStr"/>
-      <c r="AB4" s="2" t="inlineStr"/>
-      <c r="AC4" s="2" t="inlineStr">
-        <is>
-          <t>db5f8074242257836e38369f</t>
-        </is>
-      </c>
-      <c r="AD4" s="2" t="inlineStr">
-        <is>
-          <t>5f519eb5972478e4621689ff</t>
-        </is>
-      </c>
-      <c r="AE4" s="2" t="inlineStr"/>
-      <c r="AF4" s="2" t="inlineStr"/>
-      <c r="AG4" s="2" t="inlineStr"/>
-      <c r="AH4" s="2" t="inlineStr"/>
-      <c r="AI4" s="2" t="inlineStr"/>
-      <c r="AJ4" s="2" t="inlineStr"/>
-      <c r="AK4" s="2" t="inlineStr"/>
-      <c r="AL4" s="2" t="inlineStr"/>
-      <c r="AM4" s="2" t="inlineStr"/>
-      <c r="AN4" s="2" t="inlineStr"/>
-      <c r="AO4" s="2" t="inlineStr"/>
-      <c r="AP4" s="2" t="inlineStr"/>
-      <c r="AQ4" s="2" t="inlineStr"/>
-      <c r="AR4" s="2" t="inlineStr"/>
-      <c r="AS4" s="2" t="inlineStr"/>
-      <c r="AT4" s="2" t="inlineStr"/>
-      <c r="AU4" s="2" t="inlineStr"/>
-      <c r="AV4" s="2" t="inlineStr"/>
-      <c r="AW4" s="2" t="inlineStr">
+      <c r="AP4" s="3" t="inlineStr"/>
+      <c r="AQ4" s="3" t="inlineStr"/>
+      <c r="AR4" s="3" t="inlineStr"/>
+      <c r="AS4" s="3" t="inlineStr"/>
+      <c r="AT4" s="3" t="inlineStr"/>
+      <c r="AU4" s="3" t="inlineStr"/>
+      <c r="AV4" s="3" t="inlineStr"/>
+      <c r="AW4" s="3" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX4" s="2" t="inlineStr"/>
-      <c r="AY4" s="2" t="inlineStr"/>
-      <c r="AZ4" s="2" t="inlineStr"/>
-      <c r="BA4" s="2" t="inlineStr"/>
-      <c r="BB4" s="2" t="inlineStr">
+      <c r="AX4" s="3" t="inlineStr"/>
+      <c r="AY4" s="3" t="inlineStr"/>
+      <c r="AZ4" s="3" t="inlineStr"/>
+      <c r="BA4" s="3" t="inlineStr"/>
+      <c r="BB4" s="3" t="inlineStr">
         <is>
           <t>COR</t>
         </is>
       </c>
-      <c r="BC4" s="2" t="inlineStr">
+      <c r="BC4" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD4" s="2" t="inlineStr"/>
-      <c r="BE4" s="2" t="inlineStr">
+      <c r="BD4" s="3" t="inlineStr"/>
+      <c r="BE4" s="3" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF4" s="2" t="inlineStr">
+      <c r="BF4" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG4" s="2" t="inlineStr">
+      <c r="BG4" s="3" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH4" s="2" t="inlineStr"/>
+      <c r="BH4" s="3" t="inlineStr"/>
+      <c r="BI4" s="3" t="inlineStr"/>
+      <c r="BJ4" s="3" t="inlineStr"/>
+      <c r="BK4" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>BAC</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Bank of America Corporation Common Stock</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>2026-09-08T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>SEC charges Bank of America executive with insider trading</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>內線交易</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、持續追蹤</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>'-0.779</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr"/>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOdTY0bVJZYkZpb1NkbDkxWTRrXzVmWmhKOFhHcEdENDBrVVYtWDM3VWZuRXBnUk9scXFURFRkMFI3SU5Ea2lFMlZRcFp6djdlZkd0M0wtZkJjYloyeGNFdUh6RDNENWFiNnNoR1N0WUVVWEJRMm9HQlZoeEx5cWlndHVRNmVHRksyWjRjY3RYb2IwZ2o5VHFiMDFDRHc?oc=5</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>The Ticker</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr"/>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>GOVERNANCE</t>
+        </is>
+      </c>
+      <c r="Y5" s="3" t="inlineStr">
+        <is>
+          <t>INSIDER_TRADING</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>insider trading</t>
+        </is>
+      </c>
+      <c r="AA5" s="3" t="inlineStr"/>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>0d8bbb2c08644a3a866c16da943b80f0</t>
+        </is>
+      </c>
+      <c r="AC5" s="3" t="inlineStr">
+        <is>
+          <t>3f8c21c1f24e5e5792926e0e</t>
+        </is>
+      </c>
+      <c r="AD5" s="3" t="inlineStr">
+        <is>
+          <t>ee7c7a95f1fc0af1ce3dd69f</t>
+        </is>
+      </c>
+      <c r="AE5" s="3" t="inlineStr"/>
+      <c r="AF5" s="3" t="inlineStr"/>
+      <c r="AG5" s="3" t="inlineStr"/>
+      <c r="AH5" s="3" t="inlineStr"/>
+      <c r="AI5" s="3" t="inlineStr"/>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" s="3" t="inlineStr"/>
+      <c r="AM5" s="3" t="inlineStr"/>
+      <c r="AN5" s="3" t="inlineStr"/>
+      <c r="AO5" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>'-0.779</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr"/>
-      <c r="Q5" s="2" t="inlineStr"/>
-      <c r="R5" s="2" t="inlineStr"/>
-      <c r="S5" s="2" t="inlineStr"/>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOdTY0bVJZYkZpb1NkbDkxWTRrXzVmWmhKOFhHcEdENDBrVVYtWDM3VWZuRXBnUk9scXFURFRkMFI3SU5Ea2lFMlZRcFp6djdlZkd0M0wtZkJjYloyeGNFdUh6RDNENWFiNnNoR1N0WUVVWEJRMm9HQlZoeEx5cWlndHVRNmVHRksyWjRjY3RYb2IwZ2o5VHFiMDFDRHc?oc=5</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>The Ticker</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr"/>
-      <c r="X5" s="2" t="inlineStr">
-        <is>
-          <t>GOVERNANCE</t>
-        </is>
-      </c>
-      <c r="Y5" s="2" t="inlineStr">
-        <is>
-          <t>INSIDER_TRADING</t>
-        </is>
-      </c>
-      <c r="Z5" s="2" t="inlineStr">
-        <is>
-          <t>insider trading</t>
-        </is>
-      </c>
-      <c r="AA5" s="2" t="inlineStr"/>
-      <c r="AB5" s="2" t="inlineStr"/>
-      <c r="AC5" s="2" t="inlineStr">
-        <is>
-          <t>3f8c21c1f24e5e5792926e0e</t>
-        </is>
-      </c>
-      <c r="AD5" s="2" t="inlineStr">
-        <is>
-          <t>ee7c7a95f1fc0af1ce3dd69f</t>
-        </is>
-      </c>
-      <c r="AE5" s="2" t="inlineStr"/>
-      <c r="AF5" s="2" t="inlineStr"/>
-      <c r="AG5" s="2" t="inlineStr"/>
-      <c r="AH5" s="2" t="inlineStr"/>
-      <c r="AI5" s="2" t="inlineStr"/>
-      <c r="AJ5" s="2" t="inlineStr"/>
-      <c r="AK5" s="2" t="inlineStr"/>
-      <c r="AL5" s="2" t="inlineStr"/>
-      <c r="AM5" s="2" t="inlineStr"/>
-      <c r="AN5" s="2" t="inlineStr"/>
-      <c r="AO5" s="2" t="inlineStr"/>
-      <c r="AP5" s="2" t="inlineStr"/>
-      <c r="AQ5" s="2" t="inlineStr"/>
-      <c r="AR5" s="2" t="inlineStr"/>
-      <c r="AS5" s="2" t="inlineStr"/>
-      <c r="AT5" s="2" t="inlineStr"/>
-      <c r="AU5" s="2" t="inlineStr"/>
-      <c r="AV5" s="2" t="inlineStr"/>
-      <c r="AW5" s="2" t="inlineStr">
+      <c r="AP5" s="3" t="inlineStr"/>
+      <c r="AQ5" s="3" t="inlineStr"/>
+      <c r="AR5" s="3" t="inlineStr"/>
+      <c r="AS5" s="3" t="inlineStr"/>
+      <c r="AT5" s="3" t="inlineStr"/>
+      <c r="AU5" s="3" t="inlineStr"/>
+      <c r="AV5" s="3" t="inlineStr"/>
+      <c r="AW5" s="3" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX5" s="2" t="inlineStr"/>
-      <c r="AY5" s="2" t="inlineStr"/>
-      <c r="AZ5" s="2" t="inlineStr"/>
-      <c r="BA5" s="2" t="inlineStr"/>
-      <c r="BB5" s="2" t="inlineStr">
+      <c r="AX5" s="3" t="inlineStr"/>
+      <c r="AY5" s="3" t="inlineStr"/>
+      <c r="AZ5" s="3" t="inlineStr"/>
+      <c r="BA5" s="3" t="inlineStr"/>
+      <c r="BB5" s="3" t="inlineStr">
         <is>
           <t>BAC</t>
         </is>
       </c>
-      <c r="BC5" s="2" t="inlineStr">
+      <c r="BC5" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD5" s="2" t="inlineStr"/>
-      <c r="BE5" s="2" t="inlineStr">
+      <c r="BD5" s="3" t="inlineStr"/>
+      <c r="BE5" s="3" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF5" s="2" t="inlineStr">
+      <c r="BF5" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG5" s="2" t="inlineStr">
+      <c r="BG5" s="3" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH5" s="2" t="inlineStr"/>
+      <c r="BH5" s="3" t="inlineStr"/>
+      <c r="BI5" s="3" t="inlineStr"/>
+      <c r="BJ5" s="3" t="inlineStr"/>
+      <c r="BK5" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1536,28 +1640,32 @@
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>重大訴訟</t>
+          <t>隱私事件</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
+          <t>僅紀錄</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1597,7 +1705,7 @@
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>MAJOR_LITIGATION</t>
+          <t>PRIVACY_INCIDENT</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
@@ -1606,7 +1714,11 @@
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr"/>
-      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>70bd7dbdb62046198156a9ec7c4001fe</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
           <t>774f5a2fdb9372b09d92df45</t>
@@ -1627,7 +1739,11 @@
       <c r="AL6" s="2" t="inlineStr"/>
       <c r="AM6" s="2" t="inlineStr"/>
       <c r="AN6" s="2" t="inlineStr"/>
-      <c r="AO6" s="2" t="inlineStr"/>
+      <c r="AO6" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP6" s="2" t="inlineStr"/>
       <c r="AQ6" s="2" t="inlineStr"/>
       <c r="AR6" s="2" t="inlineStr"/>
@@ -1663,6 +1779,22 @@
         </is>
       </c>
       <c r="BH6" s="2" t="inlineStr"/>
+      <c r="BI6" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ6" s="2" t="inlineStr"/>
+      <c r="BK6" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1698,28 +1830,32 @@
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>監管裁罰</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1759,7 +1895,7 @@
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>REGULATORY_PENALTY</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
@@ -1768,7 +1904,11 @@
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr"/>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>11cb2fab950f4ccebbfdf048705964a7</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
           <t>1b3d79094fc5d7c367d56319</t>
@@ -1789,7 +1929,11 @@
       <c r="AL7" s="2" t="inlineStr"/>
       <c r="AM7" s="2" t="inlineStr"/>
       <c r="AN7" s="2" t="inlineStr"/>
-      <c r="AO7" s="2" t="inlineStr"/>
+      <c r="AO7" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP7" s="2" t="inlineStr"/>
       <c r="AQ7" s="2" t="inlineStr"/>
       <c r="AR7" s="2" t="inlineStr"/>
@@ -1833,6 +1977,22 @@
         </is>
       </c>
       <c r="BH7" s="2" t="inlineStr"/>
+      <c r="BI7" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ7" s="2" t="inlineStr"/>
+      <c r="BK7" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -2003,6 +2163,10 @@
         </is>
       </c>
       <c r="BH8" s="4" t="inlineStr"/>
+      <c r="BI8" s="4" t="inlineStr"/>
+      <c r="BJ8" s="4" t="inlineStr"/>
+      <c r="BK8" s="4" t="inlineStr"/>
+      <c r="BL8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -2173,6 +2337,10 @@
         </is>
       </c>
       <c r="BH9" s="4" t="inlineStr"/>
+      <c r="BI9" s="4" t="inlineStr"/>
+      <c r="BJ9" s="4" t="inlineStr"/>
+      <c r="BK9" s="4" t="inlineStr"/>
+      <c r="BL9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -2343,6 +2511,10 @@
         </is>
       </c>
       <c r="BH10" s="4" t="inlineStr"/>
+      <c r="BI10" s="4" t="inlineStr"/>
+      <c r="BJ10" s="4" t="inlineStr"/>
+      <c r="BK10" s="4" t="inlineStr"/>
+      <c r="BL10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -2505,6 +2677,10 @@
         </is>
       </c>
       <c r="BH11" s="4" t="inlineStr"/>
+      <c r="BI11" s="4" t="inlineStr"/>
+      <c r="BJ11" s="4" t="inlineStr"/>
+      <c r="BK11" s="4" t="inlineStr"/>
+      <c r="BL11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -2675,6 +2851,10 @@
         </is>
       </c>
       <c r="BH12" s="4" t="inlineStr"/>
+      <c r="BI12" s="4" t="inlineStr"/>
+      <c r="BJ12" s="4" t="inlineStr"/>
+      <c r="BK12" s="4" t="inlineStr"/>
+      <c r="BL12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -2845,1523 +3025,1563 @@
         </is>
       </c>
       <c r="BH13" s="4" t="inlineStr"/>
+      <c r="BI13" s="4" t="inlineStr"/>
+      <c r="BJ13" s="4" t="inlineStr"/>
+      <c r="BK13" s="4" t="inlineStr"/>
+      <c r="BL13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>AMGN</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Amgen Inc.</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>2026-09-08T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Amgen Shares Fall as Investors Assess Novartis Lp(a) Trial Result and BMO Downgrade</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr"/>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I14" s="3" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>分析師降評</t>
         </is>
       </c>
-      <c r="J14" s="3" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K14" s="3" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L14" s="3" t="inlineStr"/>
-      <c r="M14" s="3" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N14" s="3" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O14" s="3" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>'-0.955</t>
         </is>
       </c>
-      <c r="P14" s="3" t="inlineStr"/>
-      <c r="Q14" s="3" t="inlineStr"/>
-      <c r="R14" s="3" t="inlineStr"/>
-      <c r="S14" s="3" t="inlineStr"/>
-      <c r="T14" s="3" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U14" s="3" t="inlineStr">
+      <c r="U14" s="2" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQT2pZMUM2TlFZTEFEZ1I5UnRkbnIybkJNNE1pSDF4d01GNWdQQ1Jmb3l4SG5sUVgyYW16V0xCVm45czh6RktWejQ2QlJsYmYwSkhyd3hqSG9LdnZ2QWtRd3VzZS1QTXNNLTNNa1FhWEE3ZExRa1RtekVfcDhFaWM3cHcxWjhxVEY0aWRfRG5XYkQ1dzAwSVFldU0zSQ?oc=5</t>
         </is>
       </c>
-      <c r="V14" s="3" t="inlineStr">
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Yahoo Finance</t>
         </is>
       </c>
-      <c r="W14" s="3" t="inlineStr"/>
-      <c r="X14" s="3" t="inlineStr">
+      <c r="W14" s="2" t="inlineStr"/>
+      <c r="X14" s="2" t="inlineStr">
         <is>
           <t>MARKET</t>
         </is>
       </c>
-      <c r="Y14" s="3" t="inlineStr">
+      <c r="Y14" s="2" t="inlineStr">
         <is>
           <t>ANALYST_DOWNGRADE</t>
         </is>
       </c>
-      <c r="Z14" s="3" t="inlineStr">
+      <c r="Z14" s="2" t="inlineStr">
         <is>
           <t>downgrade</t>
         </is>
       </c>
-      <c r="AA14" s="3" t="inlineStr"/>
-      <c r="AB14" s="3" t="inlineStr"/>
-      <c r="AC14" s="3" t="inlineStr">
+      <c r="AA14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
         <is>
           <t>2fd7737902651b53746111c6</t>
         </is>
       </c>
-      <c r="AD14" s="3" t="inlineStr">
+      <c r="AD14" s="2" t="inlineStr">
         <is>
           <t>7205c96887b5b9c46b5e51e7</t>
         </is>
       </c>
-      <c r="AE14" s="3" t="inlineStr"/>
-      <c r="AF14" s="3" t="inlineStr"/>
-      <c r="AG14" s="3" t="inlineStr"/>
-      <c r="AH14" s="3" t="inlineStr"/>
-      <c r="AI14" s="3" t="inlineStr"/>
-      <c r="AJ14" s="3" t="inlineStr"/>
-      <c r="AK14" s="3" t="inlineStr"/>
-      <c r="AL14" s="3" t="inlineStr"/>
-      <c r="AM14" s="3" t="inlineStr"/>
-      <c r="AN14" s="3" t="inlineStr"/>
-      <c r="AO14" s="3" t="inlineStr"/>
-      <c r="AP14" s="3" t="inlineStr"/>
-      <c r="AQ14" s="3" t="inlineStr"/>
-      <c r="AR14" s="3" t="inlineStr"/>
-      <c r="AS14" s="3" t="inlineStr"/>
-      <c r="AT14" s="3" t="inlineStr"/>
-      <c r="AU14" s="3" t="inlineStr"/>
-      <c r="AV14" s="3" t="inlineStr"/>
-      <c r="AW14" s="3" t="inlineStr">
+      <c r="AE14" s="2" t="inlineStr"/>
+      <c r="AF14" s="2" t="inlineStr"/>
+      <c r="AG14" s="2" t="inlineStr"/>
+      <c r="AH14" s="2" t="inlineStr"/>
+      <c r="AI14" s="2" t="inlineStr"/>
+      <c r="AJ14" s="2" t="inlineStr"/>
+      <c r="AK14" s="2" t="inlineStr"/>
+      <c r="AL14" s="2" t="inlineStr"/>
+      <c r="AM14" s="2" t="inlineStr"/>
+      <c r="AN14" s="2" t="inlineStr"/>
+      <c r="AO14" s="2" t="inlineStr"/>
+      <c r="AP14" s="2" t="inlineStr"/>
+      <c r="AQ14" s="2" t="inlineStr"/>
+      <c r="AR14" s="2" t="inlineStr"/>
+      <c r="AS14" s="2" t="inlineStr"/>
+      <c r="AT14" s="2" t="inlineStr"/>
+      <c r="AU14" s="2" t="inlineStr"/>
+      <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" s="2" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX14" s="3" t="inlineStr"/>
-      <c r="AY14" s="3" t="inlineStr"/>
-      <c r="AZ14" s="3" t="inlineStr"/>
-      <c r="BA14" s="3" t="inlineStr"/>
-      <c r="BB14" s="3" t="inlineStr">
+      <c r="AX14" s="2" t="inlineStr"/>
+      <c r="AY14" s="2" t="inlineStr"/>
+      <c r="AZ14" s="2" t="inlineStr"/>
+      <c r="BA14" s="2" t="inlineStr"/>
+      <c r="BB14" s="2" t="inlineStr">
         <is>
           <t>AMGN</t>
         </is>
       </c>
-      <c r="BC14" s="3" t="inlineStr">
+      <c r="BC14" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD14" s="3" t="inlineStr"/>
-      <c r="BE14" s="3" t="inlineStr">
+      <c r="BD14" s="2" t="inlineStr"/>
+      <c r="BE14" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF14" s="3" t="inlineStr">
+      <c r="BF14" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG14" s="3" t="inlineStr">
+      <c r="BG14" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH14" s="3" t="inlineStr"/>
+      <c r="BH14" s="2" t="inlineStr"/>
+      <c r="BI14" s="2" t="inlineStr"/>
+      <c r="BJ14" s="2" t="inlineStr"/>
+      <c r="BK14" s="2" t="inlineStr"/>
+      <c r="BL14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>EBAY</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>eBay Inc.</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>2026-09-08T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>New Canada Tariffs Bring More Cross-Border Changes For eBay</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr"/>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>關稅</t>
         </is>
       </c>
-      <c r="J15" s="3" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K15" s="3" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L15" s="3" t="inlineStr"/>
-      <c r="M15" s="3" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N15" s="3" t="inlineStr">
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O15" s="3" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>0.753</t>
         </is>
       </c>
-      <c r="P15" s="3" t="inlineStr"/>
-      <c r="Q15" s="3" t="inlineStr"/>
-      <c r="R15" s="3" t="inlineStr"/>
-      <c r="S15" s="3" t="inlineStr"/>
-      <c r="T15" s="3" t="inlineStr">
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U15" s="3" t="inlineStr">
+      <c r="U15" s="2" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE1jajdMMUF0a3ByODUtalZ1U0VuR0lYSk5Wc2JqeU03M0I4UDlfZWR1alI5QWpWTjdRcGhyc080ZlRScE5YSGNlLXNONG9mdFBzTTlEeDZmb19wcDZ4dnQ3SVJ5YUk0Rkt6aGgxTFM1Qk4zRWNzV3ZWS21aNA?oc=5</t>
         </is>
       </c>
-      <c r="V15" s="3" t="inlineStr">
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Value Added Resource</t>
         </is>
       </c>
-      <c r="W15" s="3" t="inlineStr"/>
-      <c r="X15" s="3" t="inlineStr">
+      <c r="W15" s="2" t="inlineStr"/>
+      <c r="X15" s="2" t="inlineStr">
         <is>
           <t>GEOPOLITICAL</t>
         </is>
       </c>
-      <c r="Y15" s="3" t="inlineStr">
+      <c r="Y15" s="2" t="inlineStr">
         <is>
           <t>TARIFF</t>
         </is>
       </c>
-      <c r="Z15" s="3" t="inlineStr">
+      <c r="Z15" s="2" t="inlineStr">
         <is>
           <t>tariff</t>
         </is>
       </c>
-      <c r="AA15" s="3" t="inlineStr"/>
-      <c r="AB15" s="3" t="inlineStr"/>
-      <c r="AC15" s="3" t="inlineStr">
+      <c r="AA15" s="2" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
         <is>
           <t>03072db1a3750321c256aa76</t>
         </is>
       </c>
-      <c r="AD15" s="3" t="inlineStr">
+      <c r="AD15" s="2" t="inlineStr">
         <is>
           <t>6e4bd6cd0791b6ac183a9766</t>
         </is>
       </c>
-      <c r="AE15" s="3" t="inlineStr"/>
-      <c r="AF15" s="3" t="inlineStr"/>
-      <c r="AG15" s="3" t="inlineStr"/>
-      <c r="AH15" s="3" t="inlineStr"/>
-      <c r="AI15" s="3" t="inlineStr"/>
-      <c r="AJ15" s="3" t="inlineStr"/>
-      <c r="AK15" s="3" t="inlineStr"/>
-      <c r="AL15" s="3" t="inlineStr"/>
-      <c r="AM15" s="3" t="inlineStr"/>
-      <c r="AN15" s="3" t="inlineStr"/>
-      <c r="AO15" s="3" t="inlineStr"/>
-      <c r="AP15" s="3" t="inlineStr"/>
-      <c r="AQ15" s="3" t="inlineStr"/>
-      <c r="AR15" s="3" t="inlineStr"/>
-      <c r="AS15" s="3" t="inlineStr"/>
-      <c r="AT15" s="3" t="inlineStr"/>
-      <c r="AU15" s="3" t="inlineStr"/>
-      <c r="AV15" s="3" t="inlineStr"/>
-      <c r="AW15" s="3" t="inlineStr">
+      <c r="AE15" s="2" t="inlineStr"/>
+      <c r="AF15" s="2" t="inlineStr"/>
+      <c r="AG15" s="2" t="inlineStr"/>
+      <c r="AH15" s="2" t="inlineStr"/>
+      <c r="AI15" s="2" t="inlineStr"/>
+      <c r="AJ15" s="2" t="inlineStr"/>
+      <c r="AK15" s="2" t="inlineStr"/>
+      <c r="AL15" s="2" t="inlineStr"/>
+      <c r="AM15" s="2" t="inlineStr"/>
+      <c r="AN15" s="2" t="inlineStr"/>
+      <c r="AO15" s="2" t="inlineStr"/>
+      <c r="AP15" s="2" t="inlineStr"/>
+      <c r="AQ15" s="2" t="inlineStr"/>
+      <c r="AR15" s="2" t="inlineStr"/>
+      <c r="AS15" s="2" t="inlineStr"/>
+      <c r="AT15" s="2" t="inlineStr"/>
+      <c r="AU15" s="2" t="inlineStr"/>
+      <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" s="2" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX15" s="3" t="inlineStr"/>
-      <c r="AY15" s="3" t="inlineStr"/>
-      <c r="AZ15" s="3" t="inlineStr"/>
-      <c r="BA15" s="3" t="inlineStr"/>
-      <c r="BB15" s="3" t="inlineStr">
+      <c r="AX15" s="2" t="inlineStr"/>
+      <c r="AY15" s="2" t="inlineStr"/>
+      <c r="AZ15" s="2" t="inlineStr"/>
+      <c r="BA15" s="2" t="inlineStr"/>
+      <c r="BB15" s="2" t="inlineStr">
         <is>
           <t>EBAY</t>
         </is>
       </c>
-      <c r="BC15" s="3" t="inlineStr">
+      <c r="BC15" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD15" s="3" t="inlineStr"/>
-      <c r="BE15" s="3" t="inlineStr">
+      <c r="BD15" s="2" t="inlineStr"/>
+      <c r="BE15" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF15" s="3" t="inlineStr">
+      <c r="BF15" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG15" s="3" t="inlineStr">
+      <c r="BG15" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH15" s="3" t="inlineStr"/>
+      <c r="BH15" s="2" t="inlineStr"/>
+      <c r="BI15" s="2" t="inlineStr"/>
+      <c r="BJ15" s="2" t="inlineStr"/>
+      <c r="BK15" s="2" t="inlineStr"/>
+      <c r="BL15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>AMGN</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Amgen Inc.</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>2026-09-08T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Amgen: Why Rivals' Cholesterol Drug Failure Is Bad News For The Pharma (Rating Downgrade)</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr"/>
-      <c r="H16" s="3" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I16" s="3" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>分析師降評</t>
         </is>
       </c>
-      <c r="J16" s="3" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K16" s="3" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L16" s="3" t="inlineStr"/>
-      <c r="M16" s="3" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N16" s="3" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O16" s="3" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>'-0.85</t>
         </is>
       </c>
-      <c r="P16" s="3" t="inlineStr"/>
-      <c r="Q16" s="3" t="inlineStr"/>
-      <c r="R16" s="3" t="inlineStr"/>
-      <c r="S16" s="3" t="inlineStr"/>
-      <c r="T16" s="3" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U16" s="3" t="inlineStr">
+      <c r="U16" s="2" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPQjMxalRKcHVRRjZRaXBBQkV4ejJPTm8tQU8tN0ZrZGNCTXR1dXFMcFRHQXJ3VlFMc1R4WE1vTXZzdmo1LU9xeFRRS2hsT0E4dVhLc0pub09xS3JaNW9weTd2TDRrV0lRbXptM2JQZE9jN0wzNUFzeUs4T2xBNlpLZmttazRBM2dQRTNPU1BWWnRHRDlxSVRuSGtqYW5xa2JLeUxSNWlVbUpYaG5EcDJ3WnVBQzBPc0VfYTZZ?oc=5</t>
         </is>
       </c>
-      <c r="V16" s="3" t="inlineStr">
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Seeking Alpha</t>
         </is>
       </c>
-      <c r="W16" s="3" t="inlineStr"/>
-      <c r="X16" s="3" t="inlineStr">
+      <c r="W16" s="2" t="inlineStr"/>
+      <c r="X16" s="2" t="inlineStr">
         <is>
           <t>MARKET</t>
         </is>
       </c>
-      <c r="Y16" s="3" t="inlineStr">
+      <c r="Y16" s="2" t="inlineStr">
         <is>
           <t>ANALYST_DOWNGRADE</t>
         </is>
       </c>
-      <c r="Z16" s="3" t="inlineStr">
+      <c r="Z16" s="2" t="inlineStr">
         <is>
           <t>downgrade</t>
         </is>
       </c>
-      <c r="AA16" s="3" t="inlineStr"/>
-      <c r="AB16" s="3" t="inlineStr"/>
-      <c r="AC16" s="3" t="inlineStr">
+      <c r="AA16" s="2" t="inlineStr"/>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
         <is>
           <t>a4ff1c2a80c8151c4797c43a</t>
         </is>
       </c>
-      <c r="AD16" s="3" t="inlineStr">
+      <c r="AD16" s="2" t="inlineStr">
         <is>
           <t>4c87da7a8528f54ac61329e1</t>
         </is>
       </c>
-      <c r="AE16" s="3" t="inlineStr"/>
-      <c r="AF16" s="3" t="inlineStr"/>
-      <c r="AG16" s="3" t="inlineStr"/>
-      <c r="AH16" s="3" t="inlineStr"/>
-      <c r="AI16" s="3" t="inlineStr"/>
-      <c r="AJ16" s="3" t="inlineStr"/>
-      <c r="AK16" s="3" t="inlineStr"/>
-      <c r="AL16" s="3" t="inlineStr"/>
-      <c r="AM16" s="3" t="inlineStr"/>
-      <c r="AN16" s="3" t="inlineStr"/>
-      <c r="AO16" s="3" t="inlineStr"/>
-      <c r="AP16" s="3" t="inlineStr"/>
-      <c r="AQ16" s="3" t="inlineStr"/>
-      <c r="AR16" s="3" t="inlineStr"/>
-      <c r="AS16" s="3" t="inlineStr"/>
-      <c r="AT16" s="3" t="inlineStr"/>
-      <c r="AU16" s="3" t="inlineStr"/>
-      <c r="AV16" s="3" t="inlineStr"/>
-      <c r="AW16" s="3" t="inlineStr">
+      <c r="AE16" s="2" t="inlineStr"/>
+      <c r="AF16" s="2" t="inlineStr"/>
+      <c r="AG16" s="2" t="inlineStr"/>
+      <c r="AH16" s="2" t="inlineStr"/>
+      <c r="AI16" s="2" t="inlineStr"/>
+      <c r="AJ16" s="2" t="inlineStr"/>
+      <c r="AK16" s="2" t="inlineStr"/>
+      <c r="AL16" s="2" t="inlineStr"/>
+      <c r="AM16" s="2" t="inlineStr"/>
+      <c r="AN16" s="2" t="inlineStr"/>
+      <c r="AO16" s="2" t="inlineStr"/>
+      <c r="AP16" s="2" t="inlineStr"/>
+      <c r="AQ16" s="2" t="inlineStr"/>
+      <c r="AR16" s="2" t="inlineStr"/>
+      <c r="AS16" s="2" t="inlineStr"/>
+      <c r="AT16" s="2" t="inlineStr"/>
+      <c r="AU16" s="2" t="inlineStr"/>
+      <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" s="2" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX16" s="3" t="inlineStr"/>
-      <c r="AY16" s="3" t="inlineStr"/>
-      <c r="AZ16" s="3" t="inlineStr"/>
-      <c r="BA16" s="3" t="inlineStr"/>
-      <c r="BB16" s="3" t="inlineStr">
+      <c r="AX16" s="2" t="inlineStr"/>
+      <c r="AY16" s="2" t="inlineStr"/>
+      <c r="AZ16" s="2" t="inlineStr"/>
+      <c r="BA16" s="2" t="inlineStr"/>
+      <c r="BB16" s="2" t="inlineStr">
         <is>
           <t>AMGN</t>
         </is>
       </c>
-      <c r="BC16" s="3" t="inlineStr">
+      <c r="BC16" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD16" s="3" t="inlineStr"/>
-      <c r="BE16" s="3" t="inlineStr">
+      <c r="BD16" s="2" t="inlineStr"/>
+      <c r="BE16" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF16" s="3" t="inlineStr">
+      <c r="BF16" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG16" s="3" t="inlineStr">
+      <c r="BG16" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH16" s="3" t="inlineStr"/>
+      <c r="BH16" s="2" t="inlineStr"/>
+      <c r="BI16" s="2" t="inlineStr"/>
+      <c r="BJ16" s="2" t="inlineStr"/>
+      <c r="BK16" s="2" t="inlineStr"/>
+      <c r="BL16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>EIX</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Edison International Common Stock</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>2026-09-08T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Edison International gains as investors appear to reassess wildfire-risk selloff</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr"/>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I17" s="3" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>天災</t>
         </is>
       </c>
-      <c r="J17" s="3" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K17" s="3" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L17" s="3" t="inlineStr"/>
-      <c r="M17" s="3" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N17" s="3" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>0.608</t>
         </is>
       </c>
-      <c r="P17" s="3" t="inlineStr"/>
-      <c r="Q17" s="3" t="inlineStr"/>
-      <c r="R17" s="3" t="inlineStr"/>
-      <c r="S17" s="3" t="inlineStr"/>
-      <c r="T17" s="3" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U17" s="3" t="inlineStr">
+      <c r="U17" s="2" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPSFJuZFptT3BNa0syVm1aNVpVaTVRZlpVdmdJa0o4MlRheXpScnlnWF9tNFJkWUJaTjBpSmZQdzVGeWh0RVNQZF9wcGcxWENRQmp4eWI2NWtNRENPTlBVYzRKeXE0eW9oS2tXQzdfRzlyQmdydkcxZ3JuLUlodXZkdkREYTVxQTVaUjh4RHNvcnZLY2ZVdzBCeVFLaW92SHJKUWVBNzJaQ2RLSGtLS3MyelhmZw?oc=5</t>
         </is>
       </c>
-      <c r="V17" s="3" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Quiver Quantitative</t>
         </is>
       </c>
-      <c r="W17" s="3" t="inlineStr"/>
-      <c r="X17" s="3" t="inlineStr">
+      <c r="W17" s="2" t="inlineStr"/>
+      <c r="X17" s="2" t="inlineStr">
         <is>
           <t>OPERATIONS</t>
         </is>
       </c>
-      <c r="Y17" s="3" t="inlineStr">
+      <c r="Y17" s="2" t="inlineStr">
         <is>
           <t>NATURAL_DISASTER</t>
         </is>
       </c>
-      <c r="Z17" s="3" t="inlineStr">
+      <c r="Z17" s="2" t="inlineStr">
         <is>
           <t>wildfire</t>
         </is>
       </c>
-      <c r="AA17" s="3" t="inlineStr"/>
-      <c r="AB17" s="3" t="inlineStr"/>
-      <c r="AC17" s="3" t="inlineStr">
+      <c r="AA17" s="2" t="inlineStr"/>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
         <is>
           <t>dca2358d8967d9fcd9ece916</t>
         </is>
       </c>
-      <c r="AD17" s="3" t="inlineStr">
+      <c r="AD17" s="2" t="inlineStr">
         <is>
           <t>4ca4c098453740b76bcf2f0e</t>
         </is>
       </c>
-      <c r="AE17" s="3" t="inlineStr"/>
-      <c r="AF17" s="3" t="inlineStr"/>
-      <c r="AG17" s="3" t="inlineStr"/>
-      <c r="AH17" s="3" t="inlineStr"/>
-      <c r="AI17" s="3" t="inlineStr"/>
-      <c r="AJ17" s="3" t="inlineStr"/>
-      <c r="AK17" s="3" t="inlineStr"/>
-      <c r="AL17" s="3" t="inlineStr"/>
-      <c r="AM17" s="3" t="inlineStr"/>
-      <c r="AN17" s="3" t="inlineStr"/>
-      <c r="AO17" s="3" t="inlineStr"/>
-      <c r="AP17" s="3" t="inlineStr"/>
-      <c r="AQ17" s="3" t="inlineStr"/>
-      <c r="AR17" s="3" t="inlineStr"/>
-      <c r="AS17" s="3" t="inlineStr"/>
-      <c r="AT17" s="3" t="inlineStr"/>
-      <c r="AU17" s="3" t="inlineStr"/>
-      <c r="AV17" s="3" t="inlineStr"/>
-      <c r="AW17" s="3" t="inlineStr">
+      <c r="AE17" s="2" t="inlineStr"/>
+      <c r="AF17" s="2" t="inlineStr"/>
+      <c r="AG17" s="2" t="inlineStr"/>
+      <c r="AH17" s="2" t="inlineStr"/>
+      <c r="AI17" s="2" t="inlineStr"/>
+      <c r="AJ17" s="2" t="inlineStr"/>
+      <c r="AK17" s="2" t="inlineStr"/>
+      <c r="AL17" s="2" t="inlineStr"/>
+      <c r="AM17" s="2" t="inlineStr"/>
+      <c r="AN17" s="2" t="inlineStr"/>
+      <c r="AO17" s="2" t="inlineStr"/>
+      <c r="AP17" s="2" t="inlineStr"/>
+      <c r="AQ17" s="2" t="inlineStr"/>
+      <c r="AR17" s="2" t="inlineStr"/>
+      <c r="AS17" s="2" t="inlineStr"/>
+      <c r="AT17" s="2" t="inlineStr"/>
+      <c r="AU17" s="2" t="inlineStr"/>
+      <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" s="2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX17" s="3" t="inlineStr"/>
-      <c r="AY17" s="3" t="inlineStr"/>
-      <c r="AZ17" s="3" t="inlineStr"/>
-      <c r="BA17" s="3" t="inlineStr"/>
-      <c r="BB17" s="3" t="inlineStr">
+      <c r="AX17" s="2" t="inlineStr"/>
+      <c r="AY17" s="2" t="inlineStr"/>
+      <c r="AZ17" s="2" t="inlineStr"/>
+      <c r="BA17" s="2" t="inlineStr"/>
+      <c r="BB17" s="2" t="inlineStr">
         <is>
           <t>EIX</t>
         </is>
       </c>
-      <c r="BC17" s="3" t="inlineStr">
+      <c r="BC17" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD17" s="3" t="inlineStr"/>
-      <c r="BE17" s="3" t="inlineStr">
+      <c r="BD17" s="2" t="inlineStr"/>
+      <c r="BE17" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF17" s="3" t="inlineStr">
+      <c r="BF17" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG17" s="3" t="inlineStr">
+      <c r="BG17" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH17" s="3" t="inlineStr"/>
+      <c r="BH17" s="2" t="inlineStr"/>
+      <c r="BI17" s="2" t="inlineStr"/>
+      <c r="BJ17" s="2" t="inlineStr"/>
+      <c r="BK17" s="2" t="inlineStr"/>
+      <c r="BL17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>CVNA</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Carvana</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>2026-09-08T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Carvana (CVNA) Stock Could Be Overvalued Despite Its 7x Run</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr"/>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I18" s="3" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>估值疑慮</t>
         </is>
       </c>
-      <c r="J18" s="3" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K18" s="3" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L18" s="3" t="inlineStr"/>
-      <c r="M18" s="3" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N18" s="3" t="inlineStr">
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O18" s="3" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>0.597</t>
         </is>
       </c>
-      <c r="P18" s="3" t="inlineStr"/>
-      <c r="Q18" s="3" t="inlineStr"/>
-      <c r="R18" s="3" t="inlineStr"/>
-      <c r="S18" s="3" t="inlineStr"/>
-      <c r="T18" s="3" t="inlineStr">
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U18" s="3" t="inlineStr">
+      <c r="U18" s="2" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPallLNFN3LUtRazA2VTBPSFFtTzJUbTA5OHRfVnVVdUpFZEFMMTkwS1FUNnhtdXFBZnIyMGlsOVUyeFFpSlBXY25tR1h2WG5nYVFjemdUQ3hTV2MwWFdIYnpXUmxYdDZSU2dWRDVoR3RacnhqSUMyc3NjT0RXU2lyMmpWZy1JR0dNa1l3UWtHQXFBZk5PQWNpZ2k5cVF6MWVtLTQ5S1ZlcTJ2MENVdExpbjVhRHF2ZUVuV2Zr0gHAAUFVX3lxTE1Hczd0Q0FZVTJyUTlpcFhZeWdYQWd6dFo4QUNDT1RsTFZEcVdKX2RTSnRUOGgyV19XMU9iZzdheFBiamZ2UzljUXp4NGwxYVdlYlljRW1aVm1ORHBueENRb0o3Z2VjTE5OQ1VXc1RSQ2VKSGJ0bzRkVmYyZTJzc0g1Z3VPRU11b3lZVmt3a29HSGNSY3BhUHA3Z3hDdFFGOW92NmZTazV1RmJGUTNCd1d2Y1lFVTNoRUs3ZkdIMnlZcg?oc=5</t>
         </is>
       </c>
-      <c r="V18" s="3" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Simply Wall Street</t>
         </is>
       </c>
-      <c r="W18" s="3" t="inlineStr"/>
-      <c r="X18" s="3" t="inlineStr">
+      <c r="W18" s="2" t="inlineStr"/>
+      <c r="X18" s="2" t="inlineStr">
         <is>
           <t>MARKET</t>
         </is>
       </c>
-      <c r="Y18" s="3" t="inlineStr">
+      <c r="Y18" s="2" t="inlineStr">
         <is>
           <t>VALUATION_CONCERN</t>
         </is>
       </c>
-      <c r="Z18" s="3" t="inlineStr">
+      <c r="Z18" s="2" t="inlineStr">
         <is>
           <t>overvalued</t>
         </is>
       </c>
-      <c r="AA18" s="3" t="inlineStr"/>
-      <c r="AB18" s="3" t="inlineStr"/>
-      <c r="AC18" s="3" t="inlineStr">
+      <c r="AA18" s="2" t="inlineStr"/>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
         <is>
           <t>a14b2ce1a70e53f1bee1ff22</t>
         </is>
       </c>
-      <c r="AD18" s="3" t="inlineStr">
+      <c r="AD18" s="2" t="inlineStr">
         <is>
           <t>b082ada5ef455eb3edd060c7</t>
         </is>
       </c>
-      <c r="AE18" s="3" t="inlineStr"/>
-      <c r="AF18" s="3" t="inlineStr"/>
-      <c r="AG18" s="3" t="inlineStr"/>
-      <c r="AH18" s="3" t="inlineStr"/>
-      <c r="AI18" s="3" t="inlineStr"/>
-      <c r="AJ18" s="3" t="inlineStr"/>
-      <c r="AK18" s="3" t="inlineStr"/>
-      <c r="AL18" s="3" t="inlineStr"/>
-      <c r="AM18" s="3" t="inlineStr"/>
-      <c r="AN18" s="3" t="inlineStr"/>
-      <c r="AO18" s="3" t="inlineStr"/>
-      <c r="AP18" s="3" t="inlineStr"/>
-      <c r="AQ18" s="3" t="inlineStr"/>
-      <c r="AR18" s="3" t="inlineStr"/>
-      <c r="AS18" s="3" t="inlineStr"/>
-      <c r="AT18" s="3" t="inlineStr"/>
-      <c r="AU18" s="3" t="inlineStr"/>
-      <c r="AV18" s="3" t="inlineStr"/>
-      <c r="AW18" s="3" t="inlineStr"/>
-      <c r="AX18" s="3" t="inlineStr"/>
-      <c r="AY18" s="3" t="inlineStr"/>
-      <c r="AZ18" s="3" t="inlineStr"/>
-      <c r="BA18" s="3" t="inlineStr"/>
-      <c r="BB18" s="3" t="inlineStr">
+      <c r="AE18" s="2" t="inlineStr"/>
+      <c r="AF18" s="2" t="inlineStr"/>
+      <c r="AG18" s="2" t="inlineStr"/>
+      <c r="AH18" s="2" t="inlineStr"/>
+      <c r="AI18" s="2" t="inlineStr"/>
+      <c r="AJ18" s="2" t="inlineStr"/>
+      <c r="AK18" s="2" t="inlineStr"/>
+      <c r="AL18" s="2" t="inlineStr"/>
+      <c r="AM18" s="2" t="inlineStr"/>
+      <c r="AN18" s="2" t="inlineStr"/>
+      <c r="AO18" s="2" t="inlineStr"/>
+      <c r="AP18" s="2" t="inlineStr"/>
+      <c r="AQ18" s="2" t="inlineStr"/>
+      <c r="AR18" s="2" t="inlineStr"/>
+      <c r="AS18" s="2" t="inlineStr"/>
+      <c r="AT18" s="2" t="inlineStr"/>
+      <c r="AU18" s="2" t="inlineStr"/>
+      <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" s="2" t="inlineStr"/>
+      <c r="AX18" s="2" t="inlineStr"/>
+      <c r="AY18" s="2" t="inlineStr"/>
+      <c r="AZ18" s="2" t="inlineStr"/>
+      <c r="BA18" s="2" t="inlineStr"/>
+      <c r="BB18" s="2" t="inlineStr">
         <is>
           <t>CVNA</t>
         </is>
       </c>
-      <c r="BC18" s="3" t="inlineStr">
+      <c r="BC18" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD18" s="3" t="inlineStr"/>
-      <c r="BE18" s="3" t="inlineStr">
+      <c r="BD18" s="2" t="inlineStr"/>
+      <c r="BE18" s="2" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF18" s="3" t="inlineStr"/>
-      <c r="BG18" s="3" t="inlineStr">
+      <c r="BF18" s="2" t="inlineStr"/>
+      <c r="BG18" s="2" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH18" s="3" t="inlineStr"/>
+      <c r="BH18" s="2" t="inlineStr"/>
+      <c r="BI18" s="2" t="inlineStr"/>
+      <c r="BJ18" s="2" t="inlineStr"/>
+      <c r="BK18" s="2" t="inlineStr"/>
+      <c r="BL18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>DTE</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>DTE Energy</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>2026-09-08T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Detroit council seeks to lessen city's dependence on DTE Energy after tornado</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr"/>
-      <c r="H19" s="3" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I19" s="3" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>天災</t>
         </is>
       </c>
-      <c r="J19" s="3" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K19" s="3" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L19" s="3" t="inlineStr"/>
-      <c r="M19" s="3" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr"/>
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N19" s="3" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O19" s="3" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0.827</t>
         </is>
       </c>
-      <c r="P19" s="3" t="inlineStr"/>
-      <c r="Q19" s="3" t="inlineStr"/>
-      <c r="R19" s="3" t="inlineStr"/>
-      <c r="S19" s="3" t="inlineStr"/>
-      <c r="T19" s="3" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr"/>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U19" s="3" t="inlineStr">
+      <c r="U19" s="2" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMi9gFBVV95cUxQSzlSc3pXSE92dDdxcEhkRHNsckRPbnBfU2o0dEFiRUlfUUpkMTNYbDljNDRpSjZoWkJuLXlsUk5pVXVYODZ6U29vbG9EWHVqSFY2aHltYlRpLW1uUFZBQV93akRTcWI5ZFQxemFydmlLc1B4WExpeVpxWGYxSjRjaVpPak9aSzEwbEo4MjZLZjUxS29PWlU4Y1ZwalpLMFQwdFV0UzM1R29jR0JSRHR4Z3VTRHV4WnJTSUswOFZRTWdSc21WSDdHaklSRGd4cVFLWHdBOGRWc2VOMXE0T05XbmZPM2RYbFM2TDBlTjN0bXhZcmt0OVE?oc=5</t>
         </is>
       </c>
-      <c r="V19" s="3" t="inlineStr">
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>The Detroit News</t>
         </is>
       </c>
-      <c r="W19" s="3" t="inlineStr"/>
-      <c r="X19" s="3" t="inlineStr">
+      <c r="W19" s="2" t="inlineStr"/>
+      <c r="X19" s="2" t="inlineStr">
         <is>
           <t>OPERATIONS</t>
         </is>
       </c>
-      <c r="Y19" s="3" t="inlineStr">
+      <c r="Y19" s="2" t="inlineStr">
         <is>
           <t>NATURAL_DISASTER</t>
         </is>
       </c>
-      <c r="Z19" s="3" t="inlineStr">
+      <c r="Z19" s="2" t="inlineStr">
         <is>
           <t>tornado</t>
         </is>
       </c>
-      <c r="AA19" s="3" t="inlineStr"/>
-      <c r="AB19" s="3" t="inlineStr"/>
-      <c r="AC19" s="3" t="inlineStr">
+      <c r="AA19" s="2" t="inlineStr"/>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
         <is>
           <t>b532fc5ce0985281ddf048db</t>
         </is>
       </c>
-      <c r="AD19" s="3" t="inlineStr">
+      <c r="AD19" s="2" t="inlineStr">
         <is>
           <t>2716ed80d37a10b8dccdcc23</t>
         </is>
       </c>
-      <c r="AE19" s="3" t="inlineStr"/>
-      <c r="AF19" s="3" t="inlineStr"/>
-      <c r="AG19" s="3" t="inlineStr"/>
-      <c r="AH19" s="3" t="inlineStr"/>
-      <c r="AI19" s="3" t="inlineStr"/>
-      <c r="AJ19" s="3" t="inlineStr"/>
-      <c r="AK19" s="3" t="inlineStr"/>
-      <c r="AL19" s="3" t="inlineStr"/>
-      <c r="AM19" s="3" t="inlineStr"/>
-      <c r="AN19" s="3" t="inlineStr"/>
-      <c r="AO19" s="3" t="inlineStr"/>
-      <c r="AP19" s="3" t="inlineStr"/>
-      <c r="AQ19" s="3" t="inlineStr"/>
-      <c r="AR19" s="3" t="inlineStr"/>
-      <c r="AS19" s="3" t="inlineStr"/>
-      <c r="AT19" s="3" t="inlineStr"/>
-      <c r="AU19" s="3" t="inlineStr"/>
-      <c r="AV19" s="3" t="inlineStr"/>
-      <c r="AW19" s="3" t="inlineStr"/>
-      <c r="AX19" s="3" t="inlineStr"/>
-      <c r="AY19" s="3" t="inlineStr"/>
-      <c r="AZ19" s="3" t="inlineStr"/>
-      <c r="BA19" s="3" t="inlineStr"/>
-      <c r="BB19" s="3" t="inlineStr">
+      <c r="AE19" s="2" t="inlineStr"/>
+      <c r="AF19" s="2" t="inlineStr"/>
+      <c r="AG19" s="2" t="inlineStr"/>
+      <c r="AH19" s="2" t="inlineStr"/>
+      <c r="AI19" s="2" t="inlineStr"/>
+      <c r="AJ19" s="2" t="inlineStr"/>
+      <c r="AK19" s="2" t="inlineStr"/>
+      <c r="AL19" s="2" t="inlineStr"/>
+      <c r="AM19" s="2" t="inlineStr"/>
+      <c r="AN19" s="2" t="inlineStr"/>
+      <c r="AO19" s="2" t="inlineStr"/>
+      <c r="AP19" s="2" t="inlineStr"/>
+      <c r="AQ19" s="2" t="inlineStr"/>
+      <c r="AR19" s="2" t="inlineStr"/>
+      <c r="AS19" s="2" t="inlineStr"/>
+      <c r="AT19" s="2" t="inlineStr"/>
+      <c r="AU19" s="2" t="inlineStr"/>
+      <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" s="2" t="inlineStr"/>
+      <c r="AX19" s="2" t="inlineStr"/>
+      <c r="AY19" s="2" t="inlineStr"/>
+      <c r="AZ19" s="2" t="inlineStr"/>
+      <c r="BA19" s="2" t="inlineStr"/>
+      <c r="BB19" s="2" t="inlineStr">
         <is>
           <t>DTE</t>
         </is>
       </c>
-      <c r="BC19" s="3" t="inlineStr">
+      <c r="BC19" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD19" s="3" t="inlineStr"/>
-      <c r="BE19" s="3" t="inlineStr">
+      <c r="BD19" s="2" t="inlineStr"/>
+      <c r="BE19" s="2" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF19" s="3" t="inlineStr"/>
-      <c r="BG19" s="3" t="inlineStr">
+      <c r="BF19" s="2" t="inlineStr"/>
+      <c r="BG19" s="2" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH19" s="3" t="inlineStr"/>
+      <c r="BH19" s="2" t="inlineStr"/>
+      <c r="BI19" s="2" t="inlineStr"/>
+      <c r="BJ19" s="2" t="inlineStr"/>
+      <c r="BK19" s="2" t="inlineStr"/>
+      <c r="BL19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>SBUX</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Starbucks Corporation</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>2026-09-08T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>From Nike to Starbucks, Tariff Relief for Stocks Is Fleeting</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr"/>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I20" s="3" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>關稅</t>
         </is>
       </c>
-      <c r="J20" s="3" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K20" s="3" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L20" s="3" t="inlineStr"/>
-      <c r="M20" s="3" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr"/>
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N20" s="3" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O20" s="3" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0.729</t>
         </is>
       </c>
-      <c r="P20" s="3" t="inlineStr"/>
-      <c r="Q20" s="3" t="inlineStr"/>
-      <c r="R20" s="3" t="inlineStr"/>
-      <c r="S20" s="3" t="inlineStr"/>
-      <c r="T20" s="3" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr"/>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U20" s="3" t="inlineStr">
+      <c r="U20" s="2" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQOEdBN3o5UkVvQUNNd0R0MFlwUTI1dlRaOFBIMDlXdWV5Zzl1VFB1SW5tVHkzOXZCZjljcG9qU0xSV0NaN0d2TXdmMUlfRUlYVVk1dnlnS2dqVGExZW54eTM1ZDNuYWVSb0dydlhnVmJlRHg4MUI2U01hUWJmOW4ybEJCV08wa2tMUGdGd2hVanE0TXdRSnJyY2pWazdzV1VSUXdoZHFxMDQwblRzdURV?oc=5</t>
         </is>
       </c>
-      <c r="V20" s="3" t="inlineStr">
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Bloomberg.com</t>
         </is>
       </c>
-      <c r="W20" s="3" t="inlineStr"/>
-      <c r="X20" s="3" t="inlineStr">
+      <c r="W20" s="2" t="inlineStr"/>
+      <c r="X20" s="2" t="inlineStr">
         <is>
           <t>GEOPOLITICAL</t>
         </is>
       </c>
-      <c r="Y20" s="3" t="inlineStr">
+      <c r="Y20" s="2" t="inlineStr">
         <is>
           <t>TARIFF</t>
         </is>
       </c>
-      <c r="Z20" s="3" t="inlineStr">
+      <c r="Z20" s="2" t="inlineStr">
         <is>
           <t>tariff</t>
         </is>
       </c>
-      <c r="AA20" s="3" t="inlineStr"/>
-      <c r="AB20" s="3" t="inlineStr"/>
-      <c r="AC20" s="3" t="inlineStr">
+      <c r="AA20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
         <is>
           <t>610c55029de59dc5a46b4702</t>
         </is>
       </c>
-      <c r="AD20" s="3" t="inlineStr">
+      <c r="AD20" s="2" t="inlineStr">
         <is>
           <t>fcbc76b729f499f9d831f60e</t>
         </is>
       </c>
-      <c r="AE20" s="3" t="inlineStr"/>
-      <c r="AF20" s="3" t="inlineStr"/>
-      <c r="AG20" s="3" t="inlineStr"/>
-      <c r="AH20" s="3" t="inlineStr"/>
-      <c r="AI20" s="3" t="inlineStr"/>
-      <c r="AJ20" s="3" t="inlineStr"/>
-      <c r="AK20" s="3" t="inlineStr"/>
-      <c r="AL20" s="3" t="inlineStr"/>
-      <c r="AM20" s="3" t="inlineStr"/>
-      <c r="AN20" s="3" t="inlineStr"/>
-      <c r="AO20" s="3" t="inlineStr"/>
-      <c r="AP20" s="3" t="inlineStr"/>
-      <c r="AQ20" s="3" t="inlineStr"/>
-      <c r="AR20" s="3" t="inlineStr"/>
-      <c r="AS20" s="3" t="inlineStr"/>
-      <c r="AT20" s="3" t="inlineStr"/>
-      <c r="AU20" s="3" t="inlineStr"/>
-      <c r="AV20" s="3" t="inlineStr"/>
-      <c r="AW20" s="3" t="inlineStr">
+      <c r="AE20" s="2" t="inlineStr"/>
+      <c r="AF20" s="2" t="inlineStr"/>
+      <c r="AG20" s="2" t="inlineStr"/>
+      <c r="AH20" s="2" t="inlineStr"/>
+      <c r="AI20" s="2" t="inlineStr"/>
+      <c r="AJ20" s="2" t="inlineStr"/>
+      <c r="AK20" s="2" t="inlineStr"/>
+      <c r="AL20" s="2" t="inlineStr"/>
+      <c r="AM20" s="2" t="inlineStr"/>
+      <c r="AN20" s="2" t="inlineStr"/>
+      <c r="AO20" s="2" t="inlineStr"/>
+      <c r="AP20" s="2" t="inlineStr"/>
+      <c r="AQ20" s="2" t="inlineStr"/>
+      <c r="AR20" s="2" t="inlineStr"/>
+      <c r="AS20" s="2" t="inlineStr"/>
+      <c r="AT20" s="2" t="inlineStr"/>
+      <c r="AU20" s="2" t="inlineStr"/>
+      <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" s="2" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX20" s="3" t="inlineStr"/>
-      <c r="AY20" s="3" t="inlineStr"/>
-      <c r="AZ20" s="3" t="inlineStr"/>
-      <c r="BA20" s="3" t="inlineStr"/>
-      <c r="BB20" s="3" t="inlineStr">
+      <c r="AX20" s="2" t="inlineStr"/>
+      <c r="AY20" s="2" t="inlineStr"/>
+      <c r="AZ20" s="2" t="inlineStr"/>
+      <c r="BA20" s="2" t="inlineStr"/>
+      <c r="BB20" s="2" t="inlineStr">
         <is>
           <t>SBUX</t>
         </is>
       </c>
-      <c r="BC20" s="3" t="inlineStr">
+      <c r="BC20" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD20" s="3" t="inlineStr"/>
-      <c r="BE20" s="3" t="inlineStr">
+      <c r="BD20" s="2" t="inlineStr"/>
+      <c r="BE20" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF20" s="3" t="inlineStr">
+      <c r="BF20" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG20" s="3" t="inlineStr">
+      <c r="BG20" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH20" s="3" t="inlineStr"/>
+      <c r="BH20" s="2" t="inlineStr"/>
+      <c r="BI20" s="2" t="inlineStr"/>
+      <c r="BJ20" s="2" t="inlineStr"/>
+      <c r="BK20" s="2" t="inlineStr"/>
+      <c r="BL20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>AMGN</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Amgen Inc.</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>2026-09-08T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>BMO Capital Downgrades Amgen to Market Perform From Outperform, Price Target is $450</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr"/>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I21" s="3" t="inlineStr">
+      <c r="I21" s="2" t="inlineStr">
         <is>
           <t>分析師降評</t>
         </is>
       </c>
-      <c r="J21" s="3" t="inlineStr">
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K21" s="3" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L21" s="3" t="inlineStr"/>
-      <c r="M21" s="3" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr"/>
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N21" s="3" t="inlineStr">
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O21" s="3" t="inlineStr">
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>0.214</t>
         </is>
       </c>
-      <c r="P21" s="3" t="inlineStr"/>
-      <c r="Q21" s="3" t="inlineStr"/>
-      <c r="R21" s="3" t="inlineStr"/>
-      <c r="S21" s="3" t="inlineStr"/>
-      <c r="T21" s="3" t="inlineStr">
+      <c r="P21" s="2" t="inlineStr"/>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U21" s="3" t="inlineStr">
+      <c r="U21" s="2" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNdEM4TDRZTk1mMkpMZUxoaFBJQTFVanhkR3hmb2ZTQmh6OUVzZ2lkZndMUlBabGstTVg5cTNwelRWbjV4X0xUbWctbFIxeHdkVzlGcXpsd0M2UFpJeXJ2ZjJ3bjZvUU14R25RM0k2eXZqMEh2YXd0UHpreW8wd2dCX2xqVXFQbUJrTFQzd1dZeG15RUh1a0xDUmZkVURsa1hheGc?oc=5</t>
         </is>
       </c>
-      <c r="V21" s="3" t="inlineStr">
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Yahoo Finance</t>
         </is>
       </c>
-      <c r="W21" s="3" t="inlineStr"/>
-      <c r="X21" s="3" t="inlineStr">
+      <c r="W21" s="2" t="inlineStr"/>
+      <c r="X21" s="2" t="inlineStr">
         <is>
           <t>MARKET</t>
         </is>
       </c>
-      <c r="Y21" s="3" t="inlineStr">
+      <c r="Y21" s="2" t="inlineStr">
         <is>
           <t>ANALYST_DOWNGRADE</t>
         </is>
       </c>
-      <c r="Z21" s="3" t="inlineStr">
+      <c r="Z21" s="2" t="inlineStr">
         <is>
           <t>downgrade</t>
         </is>
       </c>
-      <c r="AA21" s="3" t="inlineStr"/>
-      <c r="AB21" s="3" t="inlineStr"/>
-      <c r="AC21" s="3" t="inlineStr">
+      <c r="AA21" s="2" t="inlineStr"/>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
         <is>
           <t>60ddb96394107cb28d5b4b9d</t>
         </is>
       </c>
-      <c r="AD21" s="3" t="inlineStr">
+      <c r="AD21" s="2" t="inlineStr">
         <is>
           <t>a1a71e958a3ed9fd60f65ef2</t>
         </is>
       </c>
-      <c r="AE21" s="3" t="inlineStr"/>
-      <c r="AF21" s="3" t="inlineStr"/>
-      <c r="AG21" s="3" t="inlineStr"/>
-      <c r="AH21" s="3" t="inlineStr"/>
-      <c r="AI21" s="3" t="inlineStr"/>
-      <c r="AJ21" s="3" t="inlineStr"/>
-      <c r="AK21" s="3" t="inlineStr"/>
-      <c r="AL21" s="3" t="inlineStr"/>
-      <c r="AM21" s="3" t="inlineStr"/>
-      <c r="AN21" s="3" t="inlineStr"/>
-      <c r="AO21" s="3" t="inlineStr"/>
-      <c r="AP21" s="3" t="inlineStr"/>
-      <c r="AQ21" s="3" t="inlineStr"/>
-      <c r="AR21" s="3" t="inlineStr"/>
-      <c r="AS21" s="3" t="inlineStr"/>
-      <c r="AT21" s="3" t="inlineStr"/>
-      <c r="AU21" s="3" t="inlineStr"/>
-      <c r="AV21" s="3" t="inlineStr"/>
-      <c r="AW21" s="3" t="inlineStr">
+      <c r="AE21" s="2" t="inlineStr"/>
+      <c r="AF21" s="2" t="inlineStr"/>
+      <c r="AG21" s="2" t="inlineStr"/>
+      <c r="AH21" s="2" t="inlineStr"/>
+      <c r="AI21" s="2" t="inlineStr"/>
+      <c r="AJ21" s="2" t="inlineStr"/>
+      <c r="AK21" s="2" t="inlineStr"/>
+      <c r="AL21" s="2" t="inlineStr"/>
+      <c r="AM21" s="2" t="inlineStr"/>
+      <c r="AN21" s="2" t="inlineStr"/>
+      <c r="AO21" s="2" t="inlineStr"/>
+      <c r="AP21" s="2" t="inlineStr"/>
+      <c r="AQ21" s="2" t="inlineStr"/>
+      <c r="AR21" s="2" t="inlineStr"/>
+      <c r="AS21" s="2" t="inlineStr"/>
+      <c r="AT21" s="2" t="inlineStr"/>
+      <c r="AU21" s="2" t="inlineStr"/>
+      <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" s="2" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX21" s="3" t="inlineStr"/>
-      <c r="AY21" s="3" t="inlineStr"/>
-      <c r="AZ21" s="3" t="inlineStr"/>
-      <c r="BA21" s="3" t="inlineStr"/>
-      <c r="BB21" s="3" t="inlineStr">
+      <c r="AX21" s="2" t="inlineStr"/>
+      <c r="AY21" s="2" t="inlineStr"/>
+      <c r="AZ21" s="2" t="inlineStr"/>
+      <c r="BA21" s="2" t="inlineStr"/>
+      <c r="BB21" s="2" t="inlineStr">
         <is>
           <t>AMGN</t>
         </is>
       </c>
-      <c r="BC21" s="3" t="inlineStr">
+      <c r="BC21" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD21" s="3" t="inlineStr"/>
-      <c r="BE21" s="3" t="inlineStr">
+      <c r="BD21" s="2" t="inlineStr"/>
+      <c r="BE21" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF21" s="3" t="inlineStr">
+      <c r="BF21" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG21" s="3" t="inlineStr">
+      <c r="BG21" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH21" s="3" t="inlineStr"/>
+      <c r="BH21" s="2" t="inlineStr"/>
+      <c r="BI21" s="2" t="inlineStr"/>
+      <c r="BJ21" s="2" t="inlineStr"/>
+      <c r="BK21" s="2" t="inlineStr"/>
+      <c r="BL21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>TSLA</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Tesla, Inc. </t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>2026-09-08T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>If The Macro Market Wasn't Overvalued, I'd Be All-In On Tesla (Rating Downgrade) (TSLA)</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr"/>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I22" s="3" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>分析師降評</t>
         </is>
       </c>
-      <c r="J22" s="3" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K22" s="3" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L22" s="3" t="inlineStr"/>
-      <c r="M22" s="3" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N22" s="3" t="inlineStr">
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O22" s="3" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>'-0.498</t>
         </is>
       </c>
-      <c r="P22" s="3" t="inlineStr"/>
-      <c r="Q22" s="3" t="inlineStr"/>
-      <c r="R22" s="3" t="inlineStr"/>
-      <c r="S22" s="3" t="inlineStr"/>
-      <c r="T22" s="3" t="inlineStr">
+      <c r="P22" s="2" t="inlineStr"/>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U22" s="3" t="inlineStr">
+      <c r="U22" s="2" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOeU90WHAzWW1TNTFJaXFjbUVDX3RTcE5TN1BsWWQtZ0l4NzJ1NHNVUEpSSWVwOV9rVXIwODZPRHQwT3RkRFpuZHRiUVNvYkR2cldDMG1BZnZfaXBKSVMtbXFObGVhdFFNWHd5QzdjVlh5ZmNtSFpJQUcwZzRETWg4ZGxLV2w2Si16cURudU1PQmhTcGh5SHpOYU1XZzNsOXBsVnItWWpsYzM2M2NwQi1NdHZaSE1URWs?oc=5</t>
         </is>
       </c>
-      <c r="V22" s="3" t="inlineStr">
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Seeking Alpha</t>
         </is>
       </c>
-      <c r="W22" s="3" t="inlineStr"/>
-      <c r="X22" s="3" t="inlineStr">
+      <c r="W22" s="2" t="inlineStr"/>
+      <c r="X22" s="2" t="inlineStr">
         <is>
           <t>MARKET</t>
         </is>
       </c>
-      <c r="Y22" s="3" t="inlineStr">
+      <c r="Y22" s="2" t="inlineStr">
         <is>
           <t>ANALYST_DOWNGRADE</t>
         </is>
       </c>
-      <c r="Z22" s="3" t="inlineStr">
+      <c r="Z22" s="2" t="inlineStr">
         <is>
           <t>downgrade</t>
         </is>
       </c>
-      <c r="AA22" s="3" t="inlineStr"/>
-      <c r="AB22" s="3" t="inlineStr"/>
-      <c r="AC22" s="3" t="inlineStr">
+      <c r="AA22" s="2" t="inlineStr"/>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
         <is>
           <t>01a30625f92c34a1e2ec2a92</t>
         </is>
       </c>
-      <c r="AD22" s="3" t="inlineStr">
+      <c r="AD22" s="2" t="inlineStr">
         <is>
           <t>46c3a9ad1bcc3a448d97321a</t>
         </is>
       </c>
-      <c r="AE22" s="3" t="inlineStr"/>
-      <c r="AF22" s="3" t="inlineStr"/>
-      <c r="AG22" s="3" t="inlineStr"/>
-      <c r="AH22" s="3" t="inlineStr"/>
-      <c r="AI22" s="3" t="inlineStr"/>
-      <c r="AJ22" s="3" t="inlineStr"/>
-      <c r="AK22" s="3" t="inlineStr"/>
-      <c r="AL22" s="3" t="inlineStr"/>
-      <c r="AM22" s="3" t="inlineStr"/>
-      <c r="AN22" s="3" t="inlineStr"/>
-      <c r="AO22" s="3" t="inlineStr"/>
-      <c r="AP22" s="3" t="inlineStr"/>
-      <c r="AQ22" s="3" t="inlineStr"/>
-      <c r="AR22" s="3" t="inlineStr"/>
-      <c r="AS22" s="3" t="inlineStr"/>
-      <c r="AT22" s="3" t="inlineStr"/>
-      <c r="AU22" s="3" t="inlineStr"/>
-      <c r="AV22" s="3" t="inlineStr"/>
-      <c r="AW22" s="3" t="inlineStr">
+      <c r="AE22" s="2" t="inlineStr"/>
+      <c r="AF22" s="2" t="inlineStr"/>
+      <c r="AG22" s="2" t="inlineStr"/>
+      <c r="AH22" s="2" t="inlineStr"/>
+      <c r="AI22" s="2" t="inlineStr"/>
+      <c r="AJ22" s="2" t="inlineStr"/>
+      <c r="AK22" s="2" t="inlineStr"/>
+      <c r="AL22" s="2" t="inlineStr"/>
+      <c r="AM22" s="2" t="inlineStr"/>
+      <c r="AN22" s="2" t="inlineStr"/>
+      <c r="AO22" s="2" t="inlineStr"/>
+      <c r="AP22" s="2" t="inlineStr"/>
+      <c r="AQ22" s="2" t="inlineStr"/>
+      <c r="AR22" s="2" t="inlineStr"/>
+      <c r="AS22" s="2" t="inlineStr"/>
+      <c r="AT22" s="2" t="inlineStr"/>
+      <c r="AU22" s="2" t="inlineStr"/>
+      <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" s="2" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX22" s="3" t="inlineStr"/>
-      <c r="AY22" s="3" t="inlineStr"/>
-      <c r="AZ22" s="3" t="inlineStr"/>
-      <c r="BA22" s="3" t="inlineStr"/>
-      <c r="BB22" s="3" t="inlineStr">
+      <c r="AX22" s="2" t="inlineStr"/>
+      <c r="AY22" s="2" t="inlineStr"/>
+      <c r="AZ22" s="2" t="inlineStr"/>
+      <c r="BA22" s="2" t="inlineStr"/>
+      <c r="BB22" s="2" t="inlineStr">
         <is>
           <t>TSLA</t>
         </is>
       </c>
-      <c r="BC22" s="3" t="inlineStr">
+      <c r="BC22" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD22" s="3" t="inlineStr"/>
-      <c r="BE22" s="3" t="inlineStr">
+      <c r="BD22" s="2" t="inlineStr"/>
+      <c r="BE22" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF22" s="3" t="inlineStr">
+      <c r="BF22" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG22" s="3" t="inlineStr">
+      <c r="BG22" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH22" s="3" t="inlineStr"/>
+      <c r="BH22" s="2" t="inlineStr"/>
+      <c r="BI22" s="2" t="inlineStr"/>
+      <c r="BJ22" s="2" t="inlineStr"/>
+      <c r="BK22" s="2" t="inlineStr"/>
+      <c r="BL22" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH22"/>
+  <autoFilter ref="A1:BL22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4372,7 +4592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH12"/>
+  <dimension ref="A1:BL9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4435,6 +4655,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4738,840 +4962,936 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>AMZN</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>COR</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Cencora, Inc. Common Stock</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>2026-09-08T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Nationwide Class Action Against Amazon Claims Abusive Treatment of Pregnant Warehouse Workers</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Cencora's MWI Animal Health Merger With Covetrus Sees 'Intensified' FTC Scrutiny, RBC Says</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr"/>
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>監管調查</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、持續追蹤</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O2" s="3" t="inlineStr">
+        <is>
+          <t>'-0.836</t>
+        </is>
+      </c>
+      <c r="P2" s="3" t="inlineStr"/>
+      <c r="Q2" s="3" t="inlineStr"/>
+      <c r="R2" s="3" t="inlineStr"/>
+      <c r="S2" s="3" t="inlineStr"/>
+      <c r="T2" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U2" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxQYks2S2xRUDV1SDNjTVVLNFIxR1JFeGp4NHpqekh2bV83cHhNcXFtVDhja2Y3UTgzeTczNk9wZ2dlTlFoRlZEQjNLWElWZ0hsTERPck1kNm1zaG9BTG1YRVpqaU9QODZTb3RCNTdKMVJmYWR0U0Ric3lKV0NaMENiUVRBb0djZTkxYkRPMnNXaktPTm9YbmItZG9qTHgyS0thdzN2VnFrUTFkYlZaOVdKZDU3LVNsOElkRmZxVW9EWFRhNHYyaWVxbjhsbm12TWdINHV1akpKRQ?oc=5</t>
+        </is>
+      </c>
+      <c r="V2" s="3" t="inlineStr">
+        <is>
+          <t>marketscreener.com</t>
+        </is>
+      </c>
+      <c r="W2" s="3" t="inlineStr"/>
+      <c r="X2" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y2" s="3" t="inlineStr">
+        <is>
+          <t>REGULATORY_INVESTIGATION</t>
+        </is>
+      </c>
+      <c r="Z2" s="3" t="inlineStr">
+        <is>
+          <t>FTC</t>
+        </is>
+      </c>
+      <c r="AA2" s="3" t="inlineStr"/>
+      <c r="AB2" s="3" t="inlineStr">
+        <is>
+          <t>44404b955f634b7ba8b076c5a6547b22</t>
+        </is>
+      </c>
+      <c r="AC2" s="3" t="inlineStr">
+        <is>
+          <t>db5f8074242257836e38369f</t>
+        </is>
+      </c>
+      <c r="AD2" s="3" t="inlineStr">
+        <is>
+          <t>5f519eb5972478e4621689ff</t>
+        </is>
+      </c>
+      <c r="AE2" s="3" t="inlineStr"/>
+      <c r="AF2" s="3" t="inlineStr"/>
+      <c r="AG2" s="3" t="inlineStr"/>
+      <c r="AH2" s="3" t="inlineStr"/>
+      <c r="AI2" s="3" t="inlineStr"/>
+      <c r="AJ2" s="3" t="inlineStr"/>
+      <c r="AK2" s="3" t="inlineStr"/>
+      <c r="AL2" s="3" t="inlineStr"/>
+      <c r="AM2" s="3" t="inlineStr"/>
+      <c r="AN2" s="3" t="inlineStr"/>
+      <c r="AO2" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>'-0.935</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="2" t="inlineStr"/>
-      <c r="T2" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U2" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNV3RhSFJyckF3LUpsV2dvRnc4Vy04OFp6RU5sVTZUOE1FZkdJVGozc2FUcVNiWHk0aW91c2xtSmVNeEI3eGc5OTEtcFhTSmN1LTMzbEUxOHJFY3pmdTBTMzc2Z01ycW04d3E0NTU0WVlQU2pSVE9tTDBJamVDd3dVR1o1RHpwSWdaRlZaLUR0Z0ktVmFGSzhiaHFxZmEwSW9BaG9Mc09seDJ4dXVwaVFJTzFFVzZyT3gybjJ5QTg5ek5oN0k?oc=5</t>
-        </is>
-      </c>
-      <c r="V2" s="2" t="inlineStr">
-        <is>
-          <t>A Better Balance</t>
-        </is>
-      </c>
-      <c r="W2" s="2" t="inlineStr"/>
-      <c r="X2" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y2" s="2" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z2" s="2" t="inlineStr">
-        <is>
-          <t>class action</t>
-        </is>
-      </c>
-      <c r="AA2" s="2" t="inlineStr"/>
-      <c r="AB2" s="2" t="inlineStr"/>
-      <c r="AC2" s="2" t="inlineStr">
-        <is>
-          <t>38689a87aedbe85511549073</t>
-        </is>
-      </c>
-      <c r="AD2" s="2" t="inlineStr">
-        <is>
-          <t>b545593e60d56060932416ef</t>
-        </is>
-      </c>
-      <c r="AE2" s="2" t="inlineStr"/>
-      <c r="AF2" s="2" t="inlineStr"/>
-      <c r="AG2" s="2" t="inlineStr"/>
-      <c r="AH2" s="2" t="inlineStr"/>
-      <c r="AI2" s="2" t="inlineStr"/>
-      <c r="AJ2" s="2" t="inlineStr"/>
-      <c r="AK2" s="2" t="inlineStr"/>
-      <c r="AL2" s="2" t="inlineStr"/>
-      <c r="AM2" s="2" t="inlineStr"/>
-      <c r="AN2" s="2" t="inlineStr"/>
-      <c r="AO2" s="2" t="inlineStr"/>
-      <c r="AP2" s="2" t="inlineStr"/>
-      <c r="AQ2" s="2" t="inlineStr"/>
-      <c r="AR2" s="2" t="inlineStr"/>
-      <c r="AS2" s="2" t="inlineStr"/>
-      <c r="AT2" s="2" t="inlineStr"/>
-      <c r="AU2" s="2" t="inlineStr"/>
-      <c r="AV2" s="2" t="inlineStr"/>
-      <c r="AW2" s="2" t="inlineStr"/>
-      <c r="AX2" s="2" t="inlineStr"/>
-      <c r="AY2" s="2" t="inlineStr"/>
-      <c r="AZ2" s="2" t="inlineStr"/>
-      <c r="BA2" s="2" t="inlineStr"/>
-      <c r="BB2" s="2" t="inlineStr">
-        <is>
-          <t>AMZN</t>
-        </is>
-      </c>
-      <c r="BC2" s="2" t="inlineStr">
+      <c r="AP2" s="3" t="inlineStr"/>
+      <c r="AQ2" s="3" t="inlineStr"/>
+      <c r="AR2" s="3" t="inlineStr"/>
+      <c r="AS2" s="3" t="inlineStr"/>
+      <c r="AT2" s="3" t="inlineStr"/>
+      <c r="AU2" s="3" t="inlineStr"/>
+      <c r="AV2" s="3" t="inlineStr"/>
+      <c r="AW2" s="3" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="AX2" s="3" t="inlineStr"/>
+      <c r="AY2" s="3" t="inlineStr"/>
+      <c r="AZ2" s="3" t="inlineStr"/>
+      <c r="BA2" s="3" t="inlineStr"/>
+      <c r="BB2" s="3" t="inlineStr">
+        <is>
+          <t>COR</t>
+        </is>
+      </c>
+      <c r="BC2" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD2" s="2" t="inlineStr"/>
-      <c r="BE2" s="2" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF2" s="2" t="inlineStr"/>
-      <c r="BG2" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH2" s="2" t="inlineStr"/>
+      <c r="BD2" s="3" t="inlineStr"/>
+      <c r="BE2" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
+        </is>
+      </c>
+      <c r="BG2" s="3" t="inlineStr">
+        <is>
+          <t>交易所目前名單</t>
+        </is>
+      </c>
+      <c r="BH2" s="3" t="inlineStr"/>
+      <c r="BI2" s="3" t="inlineStr"/>
+      <c r="BJ2" s="3" t="inlineStr"/>
+      <c r="BK2" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>COR</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Cencora, Inc. Common Stock</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>BAC</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Bank of America Corporation Common Stock</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>2026-09-08T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Cencora's MWI Animal Health Merger With Covetrus Sees 'Intensified' FTC Scrutiny, RBC Says</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>SEC charges Bank of America executive with insider trading</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>監管調查</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>內線交易</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、持續追蹤</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>'-0.779</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr"/>
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOdTY0bVJZYkZpb1NkbDkxWTRrXzVmWmhKOFhHcEdENDBrVVYtWDM3VWZuRXBnUk9scXFURFRkMFI3SU5Ea2lFMlZRcFp6djdlZkd0M0wtZkJjYloyeGNFdUh6RDNENWFiNnNoR1N0WUVVWEJRMm9HQlZoeEx5cWlndHVRNmVHRksyWjRjY3RYb2IwZ2o5VHFiMDFDRHc?oc=5</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>The Ticker</t>
+        </is>
+      </c>
+      <c r="W3" s="3" t="inlineStr"/>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>GOVERNANCE</t>
+        </is>
+      </c>
+      <c r="Y3" s="3" t="inlineStr">
+        <is>
+          <t>INSIDER_TRADING</t>
+        </is>
+      </c>
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>insider trading</t>
+        </is>
+      </c>
+      <c r="AA3" s="3" t="inlineStr"/>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>0d8bbb2c08644a3a866c16da943b80f0</t>
+        </is>
+      </c>
+      <c r="AC3" s="3" t="inlineStr">
+        <is>
+          <t>3f8c21c1f24e5e5792926e0e</t>
+        </is>
+      </c>
+      <c r="AD3" s="3" t="inlineStr">
+        <is>
+          <t>ee7c7a95f1fc0af1ce3dd69f</t>
+        </is>
+      </c>
+      <c r="AE3" s="3" t="inlineStr"/>
+      <c r="AF3" s="3" t="inlineStr"/>
+      <c r="AG3" s="3" t="inlineStr"/>
+      <c r="AH3" s="3" t="inlineStr"/>
+      <c r="AI3" s="3" t="inlineStr"/>
+      <c r="AJ3" s="3" t="inlineStr"/>
+      <c r="AK3" s="3" t="inlineStr"/>
+      <c r="AL3" s="3" t="inlineStr"/>
+      <c r="AM3" s="3" t="inlineStr"/>
+      <c r="AN3" s="3" t="inlineStr"/>
+      <c r="AO3" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>'-0.836</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr"/>
-      <c r="R3" s="2" t="inlineStr"/>
-      <c r="S3" s="2" t="inlineStr"/>
-      <c r="T3" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U3" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxQYks2S2xRUDV1SDNjTVVLNFIxR1JFeGp4NHpqekh2bV83cHhNcXFtVDhja2Y3UTgzeTczNk9wZ2dlTlFoRlZEQjNLWElWZ0hsTERPck1kNm1zaG9BTG1YRVpqaU9QODZTb3RCNTdKMVJmYWR0U0Ric3lKV0NaMENiUVRBb0djZTkxYkRPMnNXaktPTm9YbmItZG9qTHgyS0thdzN2VnFrUTFkYlZaOVdKZDU3LVNsOElkRmZxVW9EWFRhNHYyaWVxbjhsbm12TWdINHV1akpKRQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>marketscreener.com</t>
-        </is>
-      </c>
-      <c r="W3" s="2" t="inlineStr"/>
-      <c r="X3" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y3" s="2" t="inlineStr">
-        <is>
-          <t>REGULATORY_INVESTIGATION</t>
-        </is>
-      </c>
-      <c r="Z3" s="2" t="inlineStr">
-        <is>
-          <t>FTC</t>
-        </is>
-      </c>
-      <c r="AA3" s="2" t="inlineStr"/>
-      <c r="AB3" s="2" t="inlineStr"/>
-      <c r="AC3" s="2" t="inlineStr">
-        <is>
-          <t>db5f8074242257836e38369f</t>
-        </is>
-      </c>
-      <c r="AD3" s="2" t="inlineStr">
-        <is>
-          <t>5f519eb5972478e4621689ff</t>
-        </is>
-      </c>
-      <c r="AE3" s="2" t="inlineStr"/>
-      <c r="AF3" s="2" t="inlineStr"/>
-      <c r="AG3" s="2" t="inlineStr"/>
-      <c r="AH3" s="2" t="inlineStr"/>
-      <c r="AI3" s="2" t="inlineStr"/>
-      <c r="AJ3" s="2" t="inlineStr"/>
-      <c r="AK3" s="2" t="inlineStr"/>
-      <c r="AL3" s="2" t="inlineStr"/>
-      <c r="AM3" s="2" t="inlineStr"/>
-      <c r="AN3" s="2" t="inlineStr"/>
-      <c r="AO3" s="2" t="inlineStr"/>
-      <c r="AP3" s="2" t="inlineStr"/>
-      <c r="AQ3" s="2" t="inlineStr"/>
-      <c r="AR3" s="2" t="inlineStr"/>
-      <c r="AS3" s="2" t="inlineStr"/>
-      <c r="AT3" s="2" t="inlineStr"/>
-      <c r="AU3" s="2" t="inlineStr"/>
-      <c r="AV3" s="2" t="inlineStr"/>
-      <c r="AW3" s="2" t="inlineStr">
+      <c r="AP3" s="3" t="inlineStr"/>
+      <c r="AQ3" s="3" t="inlineStr"/>
+      <c r="AR3" s="3" t="inlineStr"/>
+      <c r="AS3" s="3" t="inlineStr"/>
+      <c r="AT3" s="3" t="inlineStr"/>
+      <c r="AU3" s="3" t="inlineStr"/>
+      <c r="AV3" s="3" t="inlineStr"/>
+      <c r="AW3" s="3" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX3" s="2" t="inlineStr"/>
-      <c r="AY3" s="2" t="inlineStr"/>
-      <c r="AZ3" s="2" t="inlineStr"/>
-      <c r="BA3" s="2" t="inlineStr"/>
-      <c r="BB3" s="2" t="inlineStr">
-        <is>
-          <t>COR</t>
-        </is>
-      </c>
-      <c r="BC3" s="2" t="inlineStr">
+      <c r="AX3" s="3" t="inlineStr"/>
+      <c r="AY3" s="3" t="inlineStr"/>
+      <c r="AZ3" s="3" t="inlineStr"/>
+      <c r="BA3" s="3" t="inlineStr"/>
+      <c r="BB3" s="3" t="inlineStr">
+        <is>
+          <t>BAC</t>
+        </is>
+      </c>
+      <c r="BC3" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD3" s="2" t="inlineStr"/>
-      <c r="BE3" s="2" t="inlineStr">
+      <c r="BD3" s="3" t="inlineStr"/>
+      <c r="BE3" s="3" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF3" s="2" t="inlineStr">
+      <c r="BF3" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG3" s="2" t="inlineStr">
+      <c r="BG3" s="3" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH3" s="2" t="inlineStr"/>
+      <c r="BH3" s="3" t="inlineStr"/>
+      <c r="BI3" s="3" t="inlineStr"/>
+      <c r="BJ3" s="3" t="inlineStr"/>
+      <c r="BK3" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>BAC</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Bank of America Corporation Common Stock</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>UBER</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Uber Technologies, Inc. Common Stock</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>2026-09-08T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>SEC charges Bank of America executive with insider trading</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>內線交易</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Uber Stock Drops 3.5%; Layoffs and London Robotaxis Put Spending in Focus</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>裁員或人力縮減</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="L4" s="4" t="inlineStr"/>
+      <c r="M4" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="N4" s="4" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>'-0.779</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr"/>
-      <c r="Q4" s="2" t="inlineStr"/>
-      <c r="R4" s="2" t="inlineStr"/>
-      <c r="S4" s="2" t="inlineStr"/>
-      <c r="T4" s="2" t="inlineStr">
+      <c r="O4" s="4" t="inlineStr">
+        <is>
+          <t>'-0.957</t>
+        </is>
+      </c>
+      <c r="P4" s="4" t="inlineStr"/>
+      <c r="Q4" s="4" t="inlineStr"/>
+      <c r="R4" s="4" t="inlineStr"/>
+      <c r="S4" s="4" t="inlineStr"/>
+      <c r="T4" s="4" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOdTY0bVJZYkZpb1NkbDkxWTRrXzVmWmhKOFhHcEdENDBrVVYtWDM3VWZuRXBnUk9scXFURFRkMFI3SU5Ea2lFMlZRcFp6djdlZkd0M0wtZkJjYloyeGNFdUh6RDNENWFiNnNoR1N0WUVVWEJRMm9HQlZoeEx5cWlndHVRNmVHRksyWjRjY3RYb2IwZ2o5VHFiMDFDRHc?oc=5</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>The Ticker</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr"/>
-      <c r="X4" s="2" t="inlineStr">
-        <is>
-          <t>GOVERNANCE</t>
-        </is>
-      </c>
-      <c r="Y4" s="2" t="inlineStr">
-        <is>
-          <t>INSIDER_TRADING</t>
-        </is>
-      </c>
-      <c r="Z4" s="2" t="inlineStr">
-        <is>
-          <t>insider trading</t>
-        </is>
-      </c>
-      <c r="AA4" s="2" t="inlineStr"/>
-      <c r="AB4" s="2" t="inlineStr"/>
-      <c r="AC4" s="2" t="inlineStr">
-        <is>
-          <t>3f8c21c1f24e5e5792926e0e</t>
-        </is>
-      </c>
-      <c r="AD4" s="2" t="inlineStr">
-        <is>
-          <t>ee7c7a95f1fc0af1ce3dd69f</t>
-        </is>
-      </c>
-      <c r="AE4" s="2" t="inlineStr"/>
-      <c r="AF4" s="2" t="inlineStr"/>
-      <c r="AG4" s="2" t="inlineStr"/>
-      <c r="AH4" s="2" t="inlineStr"/>
-      <c r="AI4" s="2" t="inlineStr"/>
-      <c r="AJ4" s="2" t="inlineStr"/>
-      <c r="AK4" s="2" t="inlineStr"/>
-      <c r="AL4" s="2" t="inlineStr"/>
-      <c r="AM4" s="2" t="inlineStr"/>
-      <c r="AN4" s="2" t="inlineStr"/>
-      <c r="AO4" s="2" t="inlineStr"/>
-      <c r="AP4" s="2" t="inlineStr"/>
-      <c r="AQ4" s="2" t="inlineStr"/>
-      <c r="AR4" s="2" t="inlineStr"/>
-      <c r="AS4" s="2" t="inlineStr"/>
-      <c r="AT4" s="2" t="inlineStr"/>
-      <c r="AU4" s="2" t="inlineStr"/>
-      <c r="AV4" s="2" t="inlineStr"/>
-      <c r="AW4" s="2" t="inlineStr">
+      <c r="U4" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNOFJ3OWRFbDhHdFBZNlhDd2lKQm1nWHlrcDhfRGlPNXY4bWNHaXoxSzBzRk5lQkxpWUN4Q0hGVXJTRml4dHpDT3F2MjJBQUxXbTRKR3pSSFFrMEhOU3pWajBDaU9RVnJLNkFBbjhPWUZHQy1ENzdtRTFHTnYtczdCeElETU1Ec1dqbk1KQWg5dFhIRmhXOGlB?oc=5</t>
+        </is>
+      </c>
+      <c r="V4" s="4" t="inlineStr">
+        <is>
+          <t>TechStock²</t>
+        </is>
+      </c>
+      <c r="W4" s="4" t="inlineStr"/>
+      <c r="X4" s="4" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y4" s="4" t="inlineStr">
+        <is>
+          <t>WORKFORCE_REDUCTION</t>
+        </is>
+      </c>
+      <c r="Z4" s="4" t="inlineStr">
+        <is>
+          <t>layoff；layoffs</t>
+        </is>
+      </c>
+      <c r="AA4" s="4" t="inlineStr"/>
+      <c r="AB4" s="4" t="inlineStr"/>
+      <c r="AC4" s="4" t="inlineStr">
+        <is>
+          <t>b8c1e2d4bf121f76b50f7cbb</t>
+        </is>
+      </c>
+      <c r="AD4" s="4" t="inlineStr">
+        <is>
+          <t>4161137925afc26be908157a</t>
+        </is>
+      </c>
+      <c r="AE4" s="4" t="inlineStr"/>
+      <c r="AF4" s="4" t="inlineStr"/>
+      <c r="AG4" s="4" t="inlineStr"/>
+      <c r="AH4" s="4" t="inlineStr"/>
+      <c r="AI4" s="4" t="inlineStr"/>
+      <c r="AJ4" s="4" t="inlineStr"/>
+      <c r="AK4" s="4" t="inlineStr"/>
+      <c r="AL4" s="4" t="inlineStr"/>
+      <c r="AM4" s="4" t="inlineStr"/>
+      <c r="AN4" s="4" t="inlineStr"/>
+      <c r="AO4" s="4" t="inlineStr"/>
+      <c r="AP4" s="4" t="inlineStr"/>
+      <c r="AQ4" s="4" t="inlineStr"/>
+      <c r="AR4" s="4" t="inlineStr"/>
+      <c r="AS4" s="4" t="inlineStr"/>
+      <c r="AT4" s="4" t="inlineStr"/>
+      <c r="AU4" s="4" t="inlineStr"/>
+      <c r="AV4" s="4" t="inlineStr"/>
+      <c r="AW4" s="4" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX4" s="2" t="inlineStr"/>
-      <c r="AY4" s="2" t="inlineStr"/>
-      <c r="AZ4" s="2" t="inlineStr"/>
-      <c r="BA4" s="2" t="inlineStr"/>
-      <c r="BB4" s="2" t="inlineStr">
-        <is>
-          <t>BAC</t>
-        </is>
-      </c>
-      <c r="BC4" s="2" t="inlineStr">
+      <c r="AX4" s="4" t="inlineStr"/>
+      <c r="AY4" s="4" t="inlineStr"/>
+      <c r="AZ4" s="4" t="inlineStr"/>
+      <c r="BA4" s="4" t="inlineStr"/>
+      <c r="BB4" s="4" t="inlineStr">
+        <is>
+          <t>UBER</t>
+        </is>
+      </c>
+      <c r="BC4" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD4" s="2" t="inlineStr"/>
-      <c r="BE4" s="2" t="inlineStr">
+      <c r="BD4" s="4" t="inlineStr"/>
+      <c r="BE4" s="4" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF4" s="2" t="inlineStr">
+      <c r="BF4" s="4" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG4" s="2" t="inlineStr">
+      <c r="BG4" s="4" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH4" s="2" t="inlineStr"/>
+      <c r="BH4" s="4" t="inlineStr"/>
+      <c r="BI4" s="4" t="inlineStr"/>
+      <c r="BJ4" s="4" t="inlineStr"/>
+      <c r="BK4" s="4" t="inlineStr"/>
+      <c r="BL4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>PYPL</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>PayPal</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>LEN</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Lennar Corporation Class A Common Stock</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>2026-09-08T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>PayPal sent private Venmo transaction data to outside companies, a new class action alleges</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Lennar data breach lawsuit takes aim at company’s lax data security</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>資料外洩</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="L5" s="4" t="inlineStr"/>
+      <c r="M5" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N5" s="4" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>'-0.494</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr"/>
-      <c r="Q5" s="2" t="inlineStr"/>
-      <c r="R5" s="2" t="inlineStr"/>
-      <c r="S5" s="2" t="inlineStr"/>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPUWZST01kWkl2RDl4UXpscGVYLVBXWUR4bEZ0SUp2V0I0WHM3NFMyNlN0U1FYQ3lKcmNKbmhiTURZNFdTSU5ITkZQRnZuU1ZINlAzd3J0MzZBRUtobnNGbXVaSWV6clhxY2dYWVBGeVNULTBBS3JXZDBjSkZUVGYwVndwSUh1ZVpuazgwVmlubFdkclpWUk0xNG9LdW1rUE9LOEQ1bk83dVNacExjeTVhZFUzT0V3SzNqR3NxV0pmZWNGQQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Claim Depot</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr"/>
-      <c r="X5" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y5" s="2" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z5" s="2" t="inlineStr">
-        <is>
-          <t>class action</t>
-        </is>
-      </c>
-      <c r="AA5" s="2" t="inlineStr"/>
-      <c r="AB5" s="2" t="inlineStr"/>
-      <c r="AC5" s="2" t="inlineStr">
-        <is>
-          <t>774f5a2fdb9372b09d92df45</t>
-        </is>
-      </c>
-      <c r="AD5" s="2" t="inlineStr">
-        <is>
-          <t>c98baec383b420596255d17b</t>
-        </is>
-      </c>
-      <c r="AE5" s="2" t="inlineStr"/>
-      <c r="AF5" s="2" t="inlineStr"/>
-      <c r="AG5" s="2" t="inlineStr"/>
-      <c r="AH5" s="2" t="inlineStr"/>
-      <c r="AI5" s="2" t="inlineStr"/>
-      <c r="AJ5" s="2" t="inlineStr"/>
-      <c r="AK5" s="2" t="inlineStr"/>
-      <c r="AL5" s="2" t="inlineStr"/>
-      <c r="AM5" s="2" t="inlineStr"/>
-      <c r="AN5" s="2" t="inlineStr"/>
-      <c r="AO5" s="2" t="inlineStr"/>
-      <c r="AP5" s="2" t="inlineStr"/>
-      <c r="AQ5" s="2" t="inlineStr"/>
-      <c r="AR5" s="2" t="inlineStr"/>
-      <c r="AS5" s="2" t="inlineStr"/>
-      <c r="AT5" s="2" t="inlineStr"/>
-      <c r="AU5" s="2" t="inlineStr"/>
-      <c r="AV5" s="2" t="inlineStr"/>
-      <c r="AW5" s="2" t="inlineStr"/>
-      <c r="AX5" s="2" t="inlineStr"/>
-      <c r="AY5" s="2" t="inlineStr"/>
-      <c r="AZ5" s="2" t="inlineStr"/>
-      <c r="BA5" s="2" t="inlineStr"/>
-      <c r="BB5" s="2" t="inlineStr">
-        <is>
-          <t>PYPL</t>
-        </is>
-      </c>
-      <c r="BC5" s="2" t="inlineStr">
+      <c r="O5" s="4" t="inlineStr">
+        <is>
+          <t>'-0.893</t>
+        </is>
+      </c>
+      <c r="P5" s="4" t="inlineStr"/>
+      <c r="Q5" s="4" t="inlineStr"/>
+      <c r="R5" s="4" t="inlineStr"/>
+      <c r="S5" s="4" t="inlineStr"/>
+      <c r="T5" s="4" t="inlineStr">
+        <is>
+          <t>原始代號與公司名稱交叉核對</t>
+        </is>
+      </c>
+      <c r="U5" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxPcVpjbjdlcDRmbUFSTXNFS2ExaVlSUkp2RTFsR0pBaWNTbGwzZHRPeHE0cE5VNDlBc3ZJUVBmY01vaUhrYjRHRlBLQ3ZrYnh2V0RfZjVFLXJrYmRTS3RVRGFpTlJ1UnpIbVdzWTU4MDhJX2szaHp3U3NkRmJtMnkxMWZsRTBFTldmMk9xWWZpam5TVlRVajJPNFoxbHpBNHVhb3BaOUJOM2tpa25xbUZTSGw0OXFWamplUVR0V3BKZzNCYzhpU2Rj?oc=5</t>
+        </is>
+      </c>
+      <c r="V5" s="4" t="inlineStr">
+        <is>
+          <t>Top Class Actions</t>
+        </is>
+      </c>
+      <c r="W5" s="4" t="inlineStr"/>
+      <c r="X5" s="4" t="inlineStr">
+        <is>
+          <t>CYBER</t>
+        </is>
+      </c>
+      <c r="Y5" s="4" t="inlineStr">
+        <is>
+          <t>DATA_BREACH</t>
+        </is>
+      </c>
+      <c r="Z5" s="4" t="inlineStr">
+        <is>
+          <t>data breach</t>
+        </is>
+      </c>
+      <c r="AA5" s="4" t="inlineStr"/>
+      <c r="AB5" s="4" t="inlineStr"/>
+      <c r="AC5" s="4" t="inlineStr">
+        <is>
+          <t>92feddbb567496d7c9a51001</t>
+        </is>
+      </c>
+      <c r="AD5" s="4" t="inlineStr">
+        <is>
+          <t>684239e1c4e7e3d7964a7f70</t>
+        </is>
+      </c>
+      <c r="AE5" s="4" t="inlineStr"/>
+      <c r="AF5" s="4" t="inlineStr"/>
+      <c r="AG5" s="4" t="inlineStr"/>
+      <c r="AH5" s="4" t="inlineStr"/>
+      <c r="AI5" s="4" t="inlineStr"/>
+      <c r="AJ5" s="4" t="inlineStr"/>
+      <c r="AK5" s="4" t="inlineStr"/>
+      <c r="AL5" s="4" t="inlineStr"/>
+      <c r="AM5" s="4" t="inlineStr"/>
+      <c r="AN5" s="4" t="inlineStr"/>
+      <c r="AO5" s="4" t="inlineStr"/>
+      <c r="AP5" s="4" t="inlineStr"/>
+      <c r="AQ5" s="4" t="inlineStr"/>
+      <c r="AR5" s="4" t="inlineStr"/>
+      <c r="AS5" s="4" t="inlineStr"/>
+      <c r="AT5" s="4" t="inlineStr"/>
+      <c r="AU5" s="4" t="inlineStr"/>
+      <c r="AV5" s="4" t="inlineStr"/>
+      <c r="AW5" s="4" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="AX5" s="4" t="inlineStr"/>
+      <c r="AY5" s="4" t="inlineStr"/>
+      <c r="AZ5" s="4" t="inlineStr"/>
+      <c r="BA5" s="4" t="inlineStr"/>
+      <c r="BB5" s="4" t="inlineStr">
+        <is>
+          <t>LEN</t>
+        </is>
+      </c>
+      <c r="BC5" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD5" s="2" t="inlineStr"/>
-      <c r="BE5" s="2" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF5" s="2" t="inlineStr"/>
-      <c r="BG5" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH5" s="2" t="inlineStr"/>
+      <c r="BD5" s="4" t="inlineStr"/>
+      <c r="BE5" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF5" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
+        </is>
+      </c>
+      <c r="BG5" s="4" t="inlineStr">
+        <is>
+          <t>交易所目前名單</t>
+        </is>
+      </c>
+      <c r="BH5" s="4" t="inlineStr"/>
+      <c r="BI5" s="4" t="inlineStr"/>
+      <c r="BJ5" s="4" t="inlineStr"/>
+      <c r="BK5" s="4" t="inlineStr"/>
+      <c r="BL5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>WMT</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Walmart Inc.</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>UBER</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Uber Technologies, Inc. Common Stock</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>2026-09-08T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Walmart settlement returns nearly $120,000 to app-based Seattle workers</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Top Uber Executive Buys $5.3 Million in Stock After Job Cuts</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>裁員或人力縮減</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="L6" s="4" t="inlineStr"/>
+      <c r="M6" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N6" s="4" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0.651</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr"/>
-      <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr"/>
-      <c r="S6" s="2" t="inlineStr"/>
-      <c r="T6" s="2" t="inlineStr">
+      <c r="O6" s="4" t="inlineStr">
+        <is>
+          <t>'-0.136</t>
+        </is>
+      </c>
+      <c r="P6" s="4" t="inlineStr"/>
+      <c r="Q6" s="4" t="inlineStr"/>
+      <c r="R6" s="4" t="inlineStr"/>
+      <c r="S6" s="4" t="inlineStr"/>
+      <c r="T6" s="4" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNUkZZS1hhMlBWaThVT3JkZVh0SDc4VWE4T1BQSS1WWEQySlUyUWVPaVBxMTktNmNEMnZCZFJvd3B1WXE4N0xsRElIenNBN2t1SGJSUU4zUEQyeE4yR044dXFsVExBUFNhallWN183VDZyUnd3SllfYTFfaXREdTRzUU1Eb25LYWtYTy1LZE1pRVNBcHlFN1V1Znh0Z211RXZOLVNaT3gzcFZMUWQ0MUdZOUw1VlVpRUVaY0dSbnVpMnVDckhwRFJzODZ0ekhDcmVSQ0R6Wg?oc=5</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>KING5.com</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr"/>
-      <c r="X6" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y6" s="2" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z6" s="2" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA6" s="2" t="inlineStr"/>
-      <c r="AB6" s="2" t="inlineStr"/>
-      <c r="AC6" s="2" t="inlineStr">
-        <is>
-          <t>1b3d79094fc5d7c367d56319</t>
-        </is>
-      </c>
-      <c r="AD6" s="2" t="inlineStr">
-        <is>
-          <t>a3022a4206556729a2b4fed0</t>
-        </is>
-      </c>
-      <c r="AE6" s="2" t="inlineStr"/>
-      <c r="AF6" s="2" t="inlineStr"/>
-      <c r="AG6" s="2" t="inlineStr"/>
-      <c r="AH6" s="2" t="inlineStr"/>
-      <c r="AI6" s="2" t="inlineStr"/>
-      <c r="AJ6" s="2" t="inlineStr"/>
-      <c r="AK6" s="2" t="inlineStr"/>
-      <c r="AL6" s="2" t="inlineStr"/>
-      <c r="AM6" s="2" t="inlineStr"/>
-      <c r="AN6" s="2" t="inlineStr"/>
-      <c r="AO6" s="2" t="inlineStr"/>
-      <c r="AP6" s="2" t="inlineStr"/>
-      <c r="AQ6" s="2" t="inlineStr"/>
-      <c r="AR6" s="2" t="inlineStr"/>
-      <c r="AS6" s="2" t="inlineStr"/>
-      <c r="AT6" s="2" t="inlineStr"/>
-      <c r="AU6" s="2" t="inlineStr"/>
-      <c r="AV6" s="2" t="inlineStr"/>
-      <c r="AW6" s="2" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
-      <c r="AX6" s="2" t="inlineStr"/>
-      <c r="AY6" s="2" t="inlineStr"/>
-      <c r="AZ6" s="2" t="inlineStr"/>
-      <c r="BA6" s="2" t="inlineStr"/>
-      <c r="BB6" s="2" t="inlineStr">
-        <is>
-          <t>WMT</t>
-        </is>
-      </c>
-      <c r="BC6" s="2" t="inlineStr">
+      <c r="U6" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE41dlAzbGVaQzNqaEpuZ1hTbjFjVXltczFmWmVkLTV3RFEycGtDbm42TDFLeVNnM2ZqakJKOTlnS01qZGFxQUk2dThFRkhqVzJjYVEyZHlYS3A2UFJSRjRXTkgxM3hMQkFIM09Gb09TOEhGOTJYSnc?oc=5</t>
+        </is>
+      </c>
+      <c r="V6" s="4" t="inlineStr">
+        <is>
+          <t>Barron's</t>
+        </is>
+      </c>
+      <c r="W6" s="4" t="inlineStr"/>
+      <c r="X6" s="4" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y6" s="4" t="inlineStr">
+        <is>
+          <t>WORKFORCE_REDUCTION</t>
+        </is>
+      </c>
+      <c r="Z6" s="4" t="inlineStr">
+        <is>
+          <t>job cuts</t>
+        </is>
+      </c>
+      <c r="AA6" s="4" t="inlineStr"/>
+      <c r="AB6" s="4" t="inlineStr"/>
+      <c r="AC6" s="4" t="inlineStr">
+        <is>
+          <t>afe86c8885c0ca93d5aeb3f5</t>
+        </is>
+      </c>
+      <c r="AD6" s="4" t="inlineStr">
+        <is>
+          <t>e5b42f025d14a0b387654dbc</t>
+        </is>
+      </c>
+      <c r="AE6" s="4" t="inlineStr"/>
+      <c r="AF6" s="4" t="inlineStr"/>
+      <c r="AG6" s="4" t="inlineStr"/>
+      <c r="AH6" s="4" t="inlineStr"/>
+      <c r="AI6" s="4" t="inlineStr"/>
+      <c r="AJ6" s="4" t="inlineStr"/>
+      <c r="AK6" s="4" t="inlineStr"/>
+      <c r="AL6" s="4" t="inlineStr"/>
+      <c r="AM6" s="4" t="inlineStr"/>
+      <c r="AN6" s="4" t="inlineStr"/>
+      <c r="AO6" s="4" t="inlineStr"/>
+      <c r="AP6" s="4" t="inlineStr"/>
+      <c r="AQ6" s="4" t="inlineStr"/>
+      <c r="AR6" s="4" t="inlineStr"/>
+      <c r="AS6" s="4" t="inlineStr"/>
+      <c r="AT6" s="4" t="inlineStr"/>
+      <c r="AU6" s="4" t="inlineStr"/>
+      <c r="AV6" s="4" t="inlineStr"/>
+      <c r="AW6" s="4" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="AX6" s="4" t="inlineStr"/>
+      <c r="AY6" s="4" t="inlineStr"/>
+      <c r="AZ6" s="4" t="inlineStr"/>
+      <c r="BA6" s="4" t="inlineStr"/>
+      <c r="BB6" s="4" t="inlineStr">
+        <is>
+          <t>UBER</t>
+        </is>
+      </c>
+      <c r="BC6" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD6" s="2" t="inlineStr"/>
-      <c r="BE6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF6" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG6" s="2" t="inlineStr">
+      <c r="BD6" s="4" t="inlineStr"/>
+      <c r="BE6" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF6" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
+        </is>
+      </c>
+      <c r="BG6" s="4" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH6" s="2" t="inlineStr"/>
+      <c r="BH6" s="4" t="inlineStr"/>
+      <c r="BI6" s="4" t="inlineStr"/>
+      <c r="BJ6" s="4" t="inlineStr"/>
+      <c r="BK6" s="4" t="inlineStr"/>
+      <c r="BL6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -5586,12 +5906,12 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Uber Technologies, Inc. Common Stock</t>
+          <t>PayPal</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -5601,7 +5921,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Uber Stock Drops 3.5%; Layoffs and London Robotaxis Put Spending in Focus</t>
+          <t>With PayPal Layoffs Brewing, How to Play PYPL Stock in September 2026</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr"/>
@@ -5638,7 +5958,7 @@
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
-          <t>'-0.957</t>
+          <t>'-0.056</t>
         </is>
       </c>
       <c r="P7" s="4" t="inlineStr"/>
@@ -5652,12 +5972,12 @@
       </c>
       <c r="U7" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNOFJ3OWRFbDhHdFBZNlhDd2lKQm1nWHlrcDhfRGlPNXY4bWNHaXoxSzBzRk5lQkxpWUN4Q0hGVXJTRml4dHpDT3F2MjJBQUxXbTRKR3pSSFFrMEhOU3pWajBDaU9RVnJLNkFBbjhPWUZHQy1ENzdtRTFHTnYtczdCeElETU1Ec1dqbk1KQWg5dFhIRmhXOGlB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNbmdTWnN1VDFxbUdhc2wzLTloNGgtTkwzMEw5Sm4wT3dhZ0Zza1hkaXVHTmR3RVdWYUhtaG9pdWdiMzI0OHh1YUxnbTZldlBrT3h2NnNFaGlGczlFUi1KdEJQVFFSRTN3Sk9EczlMaTFhMU95RWRyUzNvNHlqVjFPeWc4SW5oYVJqYmlUMzMxMkdUYmFwdk1TRHQ2VktlNlZhNFpkVnZuY0FPT2NscE9ZZVJR?oc=5</t>
         </is>
       </c>
       <c r="V7" s="4" t="inlineStr">
         <is>
-          <t>TechStock²</t>
+          <t>Barchart.com</t>
         </is>
       </c>
       <c r="W7" s="4" t="inlineStr"/>
@@ -5680,12 +6000,12 @@
       <c r="AB7" s="4" t="inlineStr"/>
       <c r="AC7" s="4" t="inlineStr">
         <is>
-          <t>b8c1e2d4bf121f76b50f7cbb</t>
+          <t>924cb1e580ddf666427b4bfe</t>
         </is>
       </c>
       <c r="AD7" s="4" t="inlineStr">
         <is>
-          <t>4161137925afc26be908157a</t>
+          <t>d2ff43426fda5fe85b0b80dd</t>
         </is>
       </c>
       <c r="AE7" s="4" t="inlineStr"/>
@@ -5706,18 +6026,14 @@
       <c r="AT7" s="4" t="inlineStr"/>
       <c r="AU7" s="4" t="inlineStr"/>
       <c r="AV7" s="4" t="inlineStr"/>
-      <c r="AW7" s="4" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
+      <c r="AW7" s="4" t="inlineStr"/>
       <c r="AX7" s="4" t="inlineStr"/>
       <c r="AY7" s="4" t="inlineStr"/>
       <c r="AZ7" s="4" t="inlineStr"/>
       <c r="BA7" s="4" t="inlineStr"/>
       <c r="BB7" s="4" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="BC7" s="4" t="inlineStr">
@@ -5728,20 +6044,20 @@
       <c r="BD7" s="4" t="inlineStr"/>
       <c r="BE7" s="4" t="inlineStr">
         <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF7" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
+          <t>公司清單</t>
+        </is>
+      </c>
+      <c r="BF7" s="4" t="inlineStr"/>
       <c r="BG7" s="4" t="inlineStr">
         <is>
-          <t>交易所目前名單</t>
+          <t>公司清單／交易所參照</t>
         </is>
       </c>
       <c r="BH7" s="4" t="inlineStr"/>
+      <c r="BI7" s="4" t="inlineStr"/>
+      <c r="BJ7" s="4" t="inlineStr"/>
+      <c r="BK7" s="4" t="inlineStr"/>
+      <c r="BL7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -5756,12 +6072,12 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>LEN</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Lennar Corporation Class A Common Stock</t>
+          <t>International Business Machines Corporation Common Stock</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -5771,7 +6087,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Lennar data breach lawsuit takes aim at company’s lax data security</t>
+          <t>IBM Executive: AI Creates Value, Not Job Cuts</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr"/>
@@ -5782,7 +6098,7 @@
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>資料外洩</t>
+          <t>裁員或人力縮減</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -5808,7 +6124,7 @@
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>'-0.893</t>
+          <t>'-0.029</t>
         </is>
       </c>
       <c r="P8" s="4" t="inlineStr"/>
@@ -5817,45 +6133,45 @@
       <c r="S8" s="4" t="inlineStr"/>
       <c r="T8" s="4" t="inlineStr">
         <is>
-          <t>原始代號與公司名稱交叉核對</t>
+          <t>公司清單／別名核對</t>
         </is>
       </c>
       <c r="U8" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxPcVpjbjdlcDRmbUFSTXNFS2ExaVlSUkp2RTFsR0pBaWNTbGwzZHRPeHE0cE5VNDlBc3ZJUVBmY01vaUhrYjRHRlBLQ3ZrYnh2V0RfZjVFLXJrYmRTS3RVRGFpTlJ1UnpIbVdzWTU4MDhJX2szaHp3U3NkRmJtMnkxMWZsRTBFTldmMk9xWWZpam5TVlRVajJPNFoxbHpBNHVhb3BaOUJOM2tpa25xbUZTSGw0OXFWamplUVR0V3BKZzNCYzhpU2Rj?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxNY3JtRmZZR3psaEZ1UE03STI0TzJGd2pfeWxSU1BoMmZvZ2JSZUZXcEpMcXhhYUstZ0htRnVia3JOQnZuekxwbVVUOXo2Z0VqM2JjeFFkbWtOSXgxOXdKbGpOUkRheHJxa3VDeUtmajZYV0dTYW43aWhuZ3lwWEhsbGY3a05yRFhk?oc=5</t>
         </is>
       </c>
       <c r="V8" s="4" t="inlineStr">
         <is>
-          <t>Top Class Actions</t>
+          <t>조선일보</t>
         </is>
       </c>
       <c r="W8" s="4" t="inlineStr"/>
       <c r="X8" s="4" t="inlineStr">
         <is>
-          <t>CYBER</t>
+          <t>OPERATIONS</t>
         </is>
       </c>
       <c r="Y8" s="4" t="inlineStr">
         <is>
-          <t>DATA_BREACH</t>
+          <t>WORKFORCE_REDUCTION</t>
         </is>
       </c>
       <c r="Z8" s="4" t="inlineStr">
         <is>
-          <t>data breach</t>
+          <t>job cuts</t>
         </is>
       </c>
       <c r="AA8" s="4" t="inlineStr"/>
       <c r="AB8" s="4" t="inlineStr"/>
       <c r="AC8" s="4" t="inlineStr">
         <is>
-          <t>92feddbb567496d7c9a51001</t>
+          <t>1f461bbf720d4b72ac19c318</t>
         </is>
       </c>
       <c r="AD8" s="4" t="inlineStr">
         <is>
-          <t>684239e1c4e7e3d7964a7f70</t>
+          <t>11da16c62ea71b43e5078a0f</t>
         </is>
       </c>
       <c r="AE8" s="4" t="inlineStr"/>
@@ -5887,7 +6203,7 @@
       <c r="BA8" s="4" t="inlineStr"/>
       <c r="BB8" s="4" t="inlineStr">
         <is>
-          <t>LEN</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="BC8" s="4" t="inlineStr">
@@ -5912,6 +6228,10 @@
         </is>
       </c>
       <c r="BH8" s="4" t="inlineStr"/>
+      <c r="BI8" s="4" t="inlineStr"/>
+      <c r="BJ8" s="4" t="inlineStr"/>
+      <c r="BK8" s="4" t="inlineStr"/>
+      <c r="BL8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -5926,12 +6246,12 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>MOS</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Uber Technologies, Inc. Common Stock</t>
+          <t>Mosaic Company (The) Common Stock</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -5941,7 +6261,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Top Uber Executive Buys $5.3 Million in Stock After Job Cuts</t>
+          <t>Partnerships Key to Strengthening Defence Supply Chain Resilience: MOS Desmond Choo at the 15th Seoul Defense Dialogue</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr"/>
@@ -5952,7 +6272,7 @@
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>裁員或人力縮減</t>
+          <t>供應鏈中斷</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -5978,7 +6298,7 @@
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>'-0.136</t>
+          <t>0.762</t>
         </is>
       </c>
       <c r="P9" s="4" t="inlineStr"/>
@@ -5992,12 +6312,12 @@
       </c>
       <c r="U9" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE41dlAzbGVaQzNqaEpuZ1hTbjFjVXltczFmWmVkLTV3RFEycGtDbm42TDFLeVNnM2ZqakJKOTlnS01qZGFxQUk2dThFRkhqVzJjYVEyZHlYS3A2UFJSRjRXTkgxM3hMQkFIM09Gb09TOEhGOTJYSnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTFA4NWJqRGFkbFd2VHBGWlItWWJPdVRNODdaYV9Bd3pWaHpMN29TaGtZTjN6dXR6ay15cjl5ZEFmam9VbFdCS2pPR2tsYV91OUUxU21zRER0V0xaOVpVZmhGVXdsZ2ttT0FheE5MWDRicTAwZ1ZRZWRiTQ?oc=5</t>
         </is>
       </c>
       <c r="V9" s="4" t="inlineStr">
         <is>
-          <t>Barron's</t>
+          <t>MINDEF Singapore</t>
         </is>
       </c>
       <c r="W9" s="4" t="inlineStr"/>
@@ -6008,24 +6328,24 @@
       </c>
       <c r="Y9" s="4" t="inlineStr">
         <is>
-          <t>WORKFORCE_REDUCTION</t>
+          <t>SUPPLY_CHAIN_DISRUPTION</t>
         </is>
       </c>
       <c r="Z9" s="4" t="inlineStr">
         <is>
-          <t>job cuts</t>
+          <t>supply chain</t>
         </is>
       </c>
       <c r="AA9" s="4" t="inlineStr"/>
       <c r="AB9" s="4" t="inlineStr"/>
       <c r="AC9" s="4" t="inlineStr">
         <is>
-          <t>afe86c8885c0ca93d5aeb3f5</t>
+          <t>9616dd333eb342415ab91203</t>
         </is>
       </c>
       <c r="AD9" s="4" t="inlineStr">
         <is>
-          <t>e5b42f025d14a0b387654dbc</t>
+          <t>32167af3504e704c5911f7dd</t>
         </is>
       </c>
       <c r="AE9" s="4" t="inlineStr"/>
@@ -6057,7 +6377,7 @@
       <c r="BA9" s="4" t="inlineStr"/>
       <c r="BB9" s="4" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>MOS</t>
         </is>
       </c>
       <c r="BC9" s="4" t="inlineStr">
@@ -6082,511 +6402,13 @@
         </is>
       </c>
       <c r="BH9" s="4" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>PYPL</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>PayPal</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-08T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>With PayPal Layoffs Brewing, How to Play PYPL Stock in September 2026</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr"/>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L10" s="4" t="inlineStr"/>
-      <c r="M10" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N10" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O10" s="4" t="inlineStr">
-        <is>
-          <t>'-0.056</t>
-        </is>
-      </c>
-      <c r="P10" s="4" t="inlineStr"/>
-      <c r="Q10" s="4" t="inlineStr"/>
-      <c r="R10" s="4" t="inlineStr"/>
-      <c r="S10" s="4" t="inlineStr"/>
-      <c r="T10" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U10" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNbmdTWnN1VDFxbUdhc2wzLTloNGgtTkwzMEw5Sm4wT3dhZ0Zza1hkaXVHTmR3RVdWYUhtaG9pdWdiMzI0OHh1YUxnbTZldlBrT3h2NnNFaGlGczlFUi1KdEJQVFFSRTN3Sk9EczlMaTFhMU95RWRyUzNvNHlqVjFPeWc4SW5oYVJqYmlUMzMxMkdUYmFwdk1TRHQ2VktlNlZhNFpkVnZuY0FPT2NscE9ZZVJR?oc=5</t>
-        </is>
-      </c>
-      <c r="V10" s="4" t="inlineStr">
-        <is>
-          <t>Barchart.com</t>
-        </is>
-      </c>
-      <c r="W10" s="4" t="inlineStr"/>
-      <c r="X10" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y10" s="4" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z10" s="4" t="inlineStr">
-        <is>
-          <t>layoff；layoffs</t>
-        </is>
-      </c>
-      <c r="AA10" s="4" t="inlineStr"/>
-      <c r="AB10" s="4" t="inlineStr"/>
-      <c r="AC10" s="4" t="inlineStr">
-        <is>
-          <t>924cb1e580ddf666427b4bfe</t>
-        </is>
-      </c>
-      <c r="AD10" s="4" t="inlineStr">
-        <is>
-          <t>d2ff43426fda5fe85b0b80dd</t>
-        </is>
-      </c>
-      <c r="AE10" s="4" t="inlineStr"/>
-      <c r="AF10" s="4" t="inlineStr"/>
-      <c r="AG10" s="4" t="inlineStr"/>
-      <c r="AH10" s="4" t="inlineStr"/>
-      <c r="AI10" s="4" t="inlineStr"/>
-      <c r="AJ10" s="4" t="inlineStr"/>
-      <c r="AK10" s="4" t="inlineStr"/>
-      <c r="AL10" s="4" t="inlineStr"/>
-      <c r="AM10" s="4" t="inlineStr"/>
-      <c r="AN10" s="4" t="inlineStr"/>
-      <c r="AO10" s="4" t="inlineStr"/>
-      <c r="AP10" s="4" t="inlineStr"/>
-      <c r="AQ10" s="4" t="inlineStr"/>
-      <c r="AR10" s="4" t="inlineStr"/>
-      <c r="AS10" s="4" t="inlineStr"/>
-      <c r="AT10" s="4" t="inlineStr"/>
-      <c r="AU10" s="4" t="inlineStr"/>
-      <c r="AV10" s="4" t="inlineStr"/>
-      <c r="AW10" s="4" t="inlineStr"/>
-      <c r="AX10" s="4" t="inlineStr"/>
-      <c r="AY10" s="4" t="inlineStr"/>
-      <c r="AZ10" s="4" t="inlineStr"/>
-      <c r="BA10" s="4" t="inlineStr"/>
-      <c r="BB10" s="4" t="inlineStr">
-        <is>
-          <t>PYPL</t>
-        </is>
-      </c>
-      <c r="BC10" s="4" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD10" s="4" t="inlineStr"/>
-      <c r="BE10" s="4" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF10" s="4" t="inlineStr"/>
-      <c r="BG10" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH10" s="4" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>IBM</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>International Business Machines Corporation Common Stock</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-08T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>IBM Executive: AI Creates Value, Not Job Cuts</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr"/>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L11" s="4" t="inlineStr"/>
-      <c r="M11" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N11" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O11" s="4" t="inlineStr">
-        <is>
-          <t>'-0.029</t>
-        </is>
-      </c>
-      <c r="P11" s="4" t="inlineStr"/>
-      <c r="Q11" s="4" t="inlineStr"/>
-      <c r="R11" s="4" t="inlineStr"/>
-      <c r="S11" s="4" t="inlineStr"/>
-      <c r="T11" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U11" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxNY3JtRmZZR3psaEZ1UE03STI0TzJGd2pfeWxSU1BoMmZvZ2JSZUZXcEpMcXhhYUstZ0htRnVia3JOQnZuekxwbVVUOXo2Z0VqM2JjeFFkbWtOSXgxOXdKbGpOUkRheHJxa3VDeUtmajZYV0dTYW43aWhuZ3lwWEhsbGY3a05yRFhk?oc=5</t>
-        </is>
-      </c>
-      <c r="V11" s="4" t="inlineStr">
-        <is>
-          <t>조선일보</t>
-        </is>
-      </c>
-      <c r="W11" s="4" t="inlineStr"/>
-      <c r="X11" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y11" s="4" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z11" s="4" t="inlineStr">
-        <is>
-          <t>job cuts</t>
-        </is>
-      </c>
-      <c r="AA11" s="4" t="inlineStr"/>
-      <c r="AB11" s="4" t="inlineStr"/>
-      <c r="AC11" s="4" t="inlineStr">
-        <is>
-          <t>1f461bbf720d4b72ac19c318</t>
-        </is>
-      </c>
-      <c r="AD11" s="4" t="inlineStr">
-        <is>
-          <t>11da16c62ea71b43e5078a0f</t>
-        </is>
-      </c>
-      <c r="AE11" s="4" t="inlineStr"/>
-      <c r="AF11" s="4" t="inlineStr"/>
-      <c r="AG11" s="4" t="inlineStr"/>
-      <c r="AH11" s="4" t="inlineStr"/>
-      <c r="AI11" s="4" t="inlineStr"/>
-      <c r="AJ11" s="4" t="inlineStr"/>
-      <c r="AK11" s="4" t="inlineStr"/>
-      <c r="AL11" s="4" t="inlineStr"/>
-      <c r="AM11" s="4" t="inlineStr"/>
-      <c r="AN11" s="4" t="inlineStr"/>
-      <c r="AO11" s="4" t="inlineStr"/>
-      <c r="AP11" s="4" t="inlineStr"/>
-      <c r="AQ11" s="4" t="inlineStr"/>
-      <c r="AR11" s="4" t="inlineStr"/>
-      <c r="AS11" s="4" t="inlineStr"/>
-      <c r="AT11" s="4" t="inlineStr"/>
-      <c r="AU11" s="4" t="inlineStr"/>
-      <c r="AV11" s="4" t="inlineStr"/>
-      <c r="AW11" s="4" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX11" s="4" t="inlineStr"/>
-      <c r="AY11" s="4" t="inlineStr"/>
-      <c r="AZ11" s="4" t="inlineStr"/>
-      <c r="BA11" s="4" t="inlineStr"/>
-      <c r="BB11" s="4" t="inlineStr">
-        <is>
-          <t>IBM</t>
-        </is>
-      </c>
-      <c r="BC11" s="4" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD11" s="4" t="inlineStr"/>
-      <c r="BE11" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF11" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG11" s="4" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH11" s="4" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>MOS</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>Mosaic Company (The) Common Stock</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-08T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>Partnerships Key to Strengthening Defence Supply Chain Resilience: MOS Desmond Choo at the 15th Seoul Defense Dialogue</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr"/>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t>供應鏈中斷</t>
-        </is>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L12" s="4" t="inlineStr"/>
-      <c r="M12" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N12" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O12" s="4" t="inlineStr">
-        <is>
-          <t>0.762</t>
-        </is>
-      </c>
-      <c r="P12" s="4" t="inlineStr"/>
-      <c r="Q12" s="4" t="inlineStr"/>
-      <c r="R12" s="4" t="inlineStr"/>
-      <c r="S12" s="4" t="inlineStr"/>
-      <c r="T12" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U12" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTFA4NWJqRGFkbFd2VHBGWlItWWJPdVRNODdaYV9Bd3pWaHpMN29TaGtZTjN6dXR6ay15cjl5ZEFmam9VbFdCS2pPR2tsYV91OUUxU21zRER0V0xaOVpVZmhGVXdsZ2ttT0FheE5MWDRicTAwZ1ZRZWRiTQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V12" s="4" t="inlineStr">
-        <is>
-          <t>MINDEF Singapore</t>
-        </is>
-      </c>
-      <c r="W12" s="4" t="inlineStr"/>
-      <c r="X12" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y12" s="4" t="inlineStr">
-        <is>
-          <t>SUPPLY_CHAIN_DISRUPTION</t>
-        </is>
-      </c>
-      <c r="Z12" s="4" t="inlineStr">
-        <is>
-          <t>supply chain</t>
-        </is>
-      </c>
-      <c r="AA12" s="4" t="inlineStr"/>
-      <c r="AB12" s="4" t="inlineStr"/>
-      <c r="AC12" s="4" t="inlineStr">
-        <is>
-          <t>9616dd333eb342415ab91203</t>
-        </is>
-      </c>
-      <c r="AD12" s="4" t="inlineStr">
-        <is>
-          <t>32167af3504e704c5911f7dd</t>
-        </is>
-      </c>
-      <c r="AE12" s="4" t="inlineStr"/>
-      <c r="AF12" s="4" t="inlineStr"/>
-      <c r="AG12" s="4" t="inlineStr"/>
-      <c r="AH12" s="4" t="inlineStr"/>
-      <c r="AI12" s="4" t="inlineStr"/>
-      <c r="AJ12" s="4" t="inlineStr"/>
-      <c r="AK12" s="4" t="inlineStr"/>
-      <c r="AL12" s="4" t="inlineStr"/>
-      <c r="AM12" s="4" t="inlineStr"/>
-      <c r="AN12" s="4" t="inlineStr"/>
-      <c r="AO12" s="4" t="inlineStr"/>
-      <c r="AP12" s="4" t="inlineStr"/>
-      <c r="AQ12" s="4" t="inlineStr"/>
-      <c r="AR12" s="4" t="inlineStr"/>
-      <c r="AS12" s="4" t="inlineStr"/>
-      <c r="AT12" s="4" t="inlineStr"/>
-      <c r="AU12" s="4" t="inlineStr"/>
-      <c r="AV12" s="4" t="inlineStr"/>
-      <c r="AW12" s="4" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX12" s="4" t="inlineStr"/>
-      <c r="AY12" s="4" t="inlineStr"/>
-      <c r="AZ12" s="4" t="inlineStr"/>
-      <c r="BA12" s="4" t="inlineStr"/>
-      <c r="BB12" s="4" t="inlineStr">
-        <is>
-          <t>MOS</t>
-        </is>
-      </c>
-      <c r="BC12" s="4" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD12" s="4" t="inlineStr"/>
-      <c r="BE12" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF12" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG12" s="4" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH12" s="4" t="inlineStr"/>
+      <c r="BI9" s="4" t="inlineStr"/>
+      <c r="BJ9" s="4" t="inlineStr"/>
+      <c r="BK9" s="4" t="inlineStr"/>
+      <c r="BL9" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH12"/>
+  <autoFilter ref="A1:BL9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6597,7 +6419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH1"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6660,6 +6482,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6963,9 +6789,29 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH1"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6976,7 +6822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH1"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7039,6 +6885,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7342,9 +7192,29 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH1"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7355,7 +7225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA5"/>
+  <dimension ref="A1:AA8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7405,477 +7275,768 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>start</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>methods</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>ai</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>started_at</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>finished_at</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>llm_calls</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>cache_reused</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>selected_company_count</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>collected</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>rows</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>errors</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>stages</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>quota_reserved</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>重複合併</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>sources</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>rows</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>changed</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>missing_publication_time</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>ticker_statuses</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>llm_calls</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>start</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>end</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>methods</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>ai</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>cache_reused</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>major</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>selected_company_count</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>collected</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>errors</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>stages</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>quota_reserved</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>重複合併</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>ticker-audit-20261024-081549</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>ticker-audit</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>daily-2026-10-26</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>schedule</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T08:15:49.296780+08:00</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T08:15:49.296790+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="G2" s="3" t="n">
-        <v>1691</v>
-      </c>
-      <c r="H2" s="3" t="n">
-        <v>257</v>
-      </c>
-      <c r="I2" s="3" t="n">
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:23:38.366332+08:00</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:40:53.776257+08:00</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="3" t="inlineStr"/>
-      <c r="M2" s="3" t="inlineStr"/>
-      <c r="N2" s="3" t="inlineStr"/>
-      <c r="O2" s="3" t="inlineStr"/>
-      <c r="P2" s="3" t="inlineStr"/>
-      <c r="Q2" s="3" t="inlineStr"/>
-      <c r="R2" s="3" t="inlineStr"/>
-      <c r="S2" s="3" t="inlineStr"/>
-      <c r="T2" s="3" t="inlineStr"/>
-      <c r="U2" s="3" t="inlineStr"/>
-      <c r="V2" s="3" t="inlineStr"/>
-      <c r="W2" s="3" t="inlineStr"/>
-      <c r="X2" s="3" t="inlineStr"/>
-      <c r="Y2" s="3" t="inlineStr"/>
-      <c r="Z2" s="3" t="inlineStr"/>
-      <c r="AA2" s="3" t="inlineStr"/>
+      <c r="M2" s="2" t="n">
+        <v>1926</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>503</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>1976</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>1961</v>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 16 筆', '方法二 1958 筆；公司 503 家（非輪替）', '市場事件搜尋 2 筆', 'FinBERT 完成 1976 筆']</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="V2" s="2" t="n">
+        <v>1961</v>
+      </c>
+      <c r="W2" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="X2" s="2" t="inlineStr"/>
+      <c r="Y2" s="2" t="inlineStr"/>
+      <c r="Z2" s="2" t="inlineStr"/>
+      <c r="AA2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>daily-2026-10-25</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>schedule</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:26:34.299718+08:00</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:32:11.776786+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
-      <c r="J3" s="3" t="inlineStr"/>
-      <c r="K3" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-22T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr"/>
-      <c r="P3" s="3" t="b">
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="Q3" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="R3" s="3" t="n">
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:23:17.137147+08:00</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:40:12.120180+08:00</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="S3" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="T3" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="U3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" s="3" t="inlineStr">
+      <c r="M3" s="2" t="n">
+        <v>2032</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>503</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>2089</v>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>2067</v>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="X3" s="3" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
-      </c>
-      <c r="Y3" s="3" t="n">
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 26 筆', '方法二 2059 筆；公司 503 家（非輪替）', '市場事件搜尋 6 筆', 'FinBERT 完成 2089 筆']</t>
+        </is>
+      </c>
+      <c r="U3" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="Z3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="V3" s="2" t="n">
+        <v>2067</v>
+      </c>
+      <c r="W3" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="X3" s="2" t="inlineStr"/>
+      <c r="Y3" s="2" t="inlineStr"/>
+      <c r="Z3" s="2" t="inlineStr"/>
+      <c r="AA3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>daily-2026-10-24</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>schedule</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:20:47.845317+08:00</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:21:20.302846+08:00</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr"/>
-      <c r="G4" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
-      <c r="J4" s="3" t="inlineStr"/>
-      <c r="K4" s="3" t="n">
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="S4" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="T4" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="U4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="V4" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="W4" s="3" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T12:44:09.884829+08:00</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T13:04:34.984103+08:00</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>3760</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>503</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>3802</v>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>3825</v>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="X4" s="3" t="inlineStr">
-        <is>
-          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
-        </is>
-      </c>
-      <c r="Y4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA4" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 158 筆', '方法二 3638 筆；公司 503 家（非輪替）', '市場事件搜尋 8 筆', 'FinBERT 完成 3802 筆']</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="V4" s="2" t="n">
+        <v>3793</v>
+      </c>
+      <c r="W4" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="X4" s="2" t="inlineStr"/>
+      <c r="Y4" s="2" t="inlineStr"/>
+      <c r="Z4" s="2" t="inlineStr"/>
+      <c r="AA4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>ticker-audit-20261024-081549</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>ticker-audit</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296780+08:00</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296790+08:00</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr"/>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr"/>
+      <c r="R5" s="2" t="n">
+        <v>1691</v>
+      </c>
+      <c r="S5" s="2" t="inlineStr"/>
+      <c r="T5" s="2" t="inlineStr"/>
+      <c r="U5" s="2" t="inlineStr"/>
+      <c r="V5" s="2" t="inlineStr"/>
+      <c r="W5" s="2" t="inlineStr"/>
+      <c r="X5" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y5" s="2" t="n">
+        <v>257</v>
+      </c>
+      <c r="Z5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
+          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:34.299718+08:00</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:32:11.776786+08:00</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="V6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="2" t="inlineStr"/>
+      <c r="Y6" s="2" t="inlineStr"/>
+      <c r="Z6" s="2" t="inlineStr"/>
+      <c r="AA6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:20:47.845317+08:00</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:21:20.302846+08:00</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="W7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="2" t="inlineStr"/>
+      <c r="Y7" s="2" t="inlineStr"/>
+      <c r="Z7" s="2" t="inlineStr"/>
+      <c r="AA7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:19:11.949238+08:00</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:19:18.833437+08:00</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="n">
+      <c r="K8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr"/>
-      <c r="J5" s="3" t="inlineStr"/>
-      <c r="K5" s="3" t="n">
+      <c r="M8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="b">
+      <c r="N8" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q5" s="3" t="n">
-        <v>33</v>
-      </c>
-      <c r="R5" s="3" t="n">
+      <c r="V8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="S5" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="T5" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="U5" s="3" t="n">
+      <c r="W8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X5" s="3" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
-      </c>
-      <c r="Y5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="X8" s="2" t="inlineStr"/>
+      <c r="Y8" s="2" t="inlineStr"/>
+      <c r="Z8" s="2" t="inlineStr"/>
+      <c r="AA8" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA5"/>
+  <autoFilter ref="A1:AA8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/news_daily/2026-09-08.xlsx
+++ b/news_daily/2026-09-08.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$22</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
@@ -2043,13 +2043,17 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L8" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
@@ -2098,7 +2102,11 @@
         </is>
       </c>
       <c r="AA8" s="4" t="inlineStr"/>
-      <c r="AB8" s="4" t="inlineStr"/>
+      <c r="AB8" s="4" t="inlineStr">
+        <is>
+          <t>6e48a6637e46437b9a5183851b9eb389</t>
+        </is>
+      </c>
       <c r="AC8" s="4" t="inlineStr">
         <is>
           <t>b8c1e2d4bf121f76b50f7cbb</t>
@@ -2119,7 +2127,11 @@
       <c r="AL8" s="4" t="inlineStr"/>
       <c r="AM8" s="4" t="inlineStr"/>
       <c r="AN8" s="4" t="inlineStr"/>
-      <c r="AO8" s="4" t="inlineStr"/>
+      <c r="AO8" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP8" s="4" t="inlineStr"/>
       <c r="AQ8" s="4" t="inlineStr"/>
       <c r="AR8" s="4" t="inlineStr"/>
@@ -2165,8 +2177,16 @@
       <c r="BH8" s="4" t="inlineStr"/>
       <c r="BI8" s="4" t="inlineStr"/>
       <c r="BJ8" s="4" t="inlineStr"/>
-      <c r="BK8" s="4" t="inlineStr"/>
-      <c r="BL8" s="4" t="inlineStr"/>
+      <c r="BK8" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL8" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -2217,13 +2237,17 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L9" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
@@ -2272,7 +2296,11 @@
         </is>
       </c>
       <c r="AA9" s="4" t="inlineStr"/>
-      <c r="AB9" s="4" t="inlineStr"/>
+      <c r="AB9" s="4" t="inlineStr">
+        <is>
+          <t>8de77b64f76b44bc9118522a8f683454</t>
+        </is>
+      </c>
       <c r="AC9" s="4" t="inlineStr">
         <is>
           <t>92feddbb567496d7c9a51001</t>
@@ -2293,7 +2321,11 @@
       <c r="AL9" s="4" t="inlineStr"/>
       <c r="AM9" s="4" t="inlineStr"/>
       <c r="AN9" s="4" t="inlineStr"/>
-      <c r="AO9" s="4" t="inlineStr"/>
+      <c r="AO9" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP9" s="4" t="inlineStr"/>
       <c r="AQ9" s="4" t="inlineStr"/>
       <c r="AR9" s="4" t="inlineStr"/>
@@ -2339,182 +2371,214 @@
       <c r="BH9" s="4" t="inlineStr"/>
       <c r="BI9" s="4" t="inlineStr"/>
       <c r="BJ9" s="4" t="inlineStr"/>
-      <c r="BK9" s="4" t="inlineStr"/>
-      <c r="BL9" s="4" t="inlineStr"/>
+      <c r="BK9" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL9" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UBER</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Uber Technologies, Inc. Common Stock</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>2026-09-08T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Top Uber Executive Buys $5.3 Million in Stock After Job Cuts</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr"/>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L10" s="4" t="inlineStr"/>
-      <c r="M10" s="4" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>'-0.136</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE41dlAzbGVaQzNqaEpuZ1hTbjFjVXltczFmWmVkLTV3RFEycGtDbm42TDFLeVNnM2ZqakJKOTlnS01qZGFxQUk2dThFRkhqVzJjYVEyZHlYS3A2UFJSRjRXTkgxM3hMQkFIM09Gb09TOEhGOTJYSnc?oc=5</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Barron's</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr"/>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>job cuts</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>e2b8fcf8e1fc44339892a836a122a448</t>
+        </is>
+      </c>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>afe86c8885c0ca93d5aeb3f5</t>
+        </is>
+      </c>
+      <c r="AD10" s="2" t="inlineStr">
+        <is>
+          <t>e5b42f025d14a0b387654dbc</t>
+        </is>
+      </c>
+      <c r="AE10" s="2" t="inlineStr"/>
+      <c r="AF10" s="2" t="inlineStr"/>
+      <c r="AG10" s="2" t="inlineStr"/>
+      <c r="AH10" s="2" t="inlineStr"/>
+      <c r="AI10" s="2" t="inlineStr"/>
+      <c r="AJ10" s="2" t="inlineStr"/>
+      <c r="AK10" s="2" t="inlineStr"/>
+      <c r="AL10" s="2" t="inlineStr"/>
+      <c r="AM10" s="2" t="inlineStr"/>
+      <c r="AN10" s="2" t="inlineStr"/>
+      <c r="AO10" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N10" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O10" s="4" t="inlineStr">
-        <is>
-          <t>'-0.136</t>
-        </is>
-      </c>
-      <c r="P10" s="4" t="inlineStr"/>
-      <c r="Q10" s="4" t="inlineStr"/>
-      <c r="R10" s="4" t="inlineStr"/>
-      <c r="S10" s="4" t="inlineStr"/>
-      <c r="T10" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U10" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE41dlAzbGVaQzNqaEpuZ1hTbjFjVXltczFmWmVkLTV3RFEycGtDbm42TDFLeVNnM2ZqakJKOTlnS01qZGFxQUk2dThFRkhqVzJjYVEyZHlYS3A2UFJSRjRXTkgxM3hMQkFIM09Gb09TOEhGOTJYSnc?oc=5</t>
-        </is>
-      </c>
-      <c r="V10" s="4" t="inlineStr">
-        <is>
-          <t>Barron's</t>
-        </is>
-      </c>
-      <c r="W10" s="4" t="inlineStr"/>
-      <c r="X10" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y10" s="4" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z10" s="4" t="inlineStr">
-        <is>
-          <t>job cuts</t>
-        </is>
-      </c>
-      <c r="AA10" s="4" t="inlineStr"/>
-      <c r="AB10" s="4" t="inlineStr"/>
-      <c r="AC10" s="4" t="inlineStr">
-        <is>
-          <t>afe86c8885c0ca93d5aeb3f5</t>
-        </is>
-      </c>
-      <c r="AD10" s="4" t="inlineStr">
-        <is>
-          <t>e5b42f025d14a0b387654dbc</t>
-        </is>
-      </c>
-      <c r="AE10" s="4" t="inlineStr"/>
-      <c r="AF10" s="4" t="inlineStr"/>
-      <c r="AG10" s="4" t="inlineStr"/>
-      <c r="AH10" s="4" t="inlineStr"/>
-      <c r="AI10" s="4" t="inlineStr"/>
-      <c r="AJ10" s="4" t="inlineStr"/>
-      <c r="AK10" s="4" t="inlineStr"/>
-      <c r="AL10" s="4" t="inlineStr"/>
-      <c r="AM10" s="4" t="inlineStr"/>
-      <c r="AN10" s="4" t="inlineStr"/>
-      <c r="AO10" s="4" t="inlineStr"/>
-      <c r="AP10" s="4" t="inlineStr"/>
-      <c r="AQ10" s="4" t="inlineStr"/>
-      <c r="AR10" s="4" t="inlineStr"/>
-      <c r="AS10" s="4" t="inlineStr"/>
-      <c r="AT10" s="4" t="inlineStr"/>
-      <c r="AU10" s="4" t="inlineStr"/>
-      <c r="AV10" s="4" t="inlineStr"/>
-      <c r="AW10" s="4" t="inlineStr">
+      <c r="AP10" s="2" t="inlineStr"/>
+      <c r="AQ10" s="2" t="inlineStr"/>
+      <c r="AR10" s="2" t="inlineStr"/>
+      <c r="AS10" s="2" t="inlineStr"/>
+      <c r="AT10" s="2" t="inlineStr"/>
+      <c r="AU10" s="2" t="inlineStr"/>
+      <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" s="2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX10" s="4" t="inlineStr"/>
-      <c r="AY10" s="4" t="inlineStr"/>
-      <c r="AZ10" s="4" t="inlineStr"/>
-      <c r="BA10" s="4" t="inlineStr"/>
-      <c r="BB10" s="4" t="inlineStr">
+      <c r="AX10" s="2" t="inlineStr"/>
+      <c r="AY10" s="2" t="inlineStr"/>
+      <c r="AZ10" s="2" t="inlineStr"/>
+      <c r="BA10" s="2" t="inlineStr"/>
+      <c r="BB10" s="2" t="inlineStr">
         <is>
           <t>UBER</t>
         </is>
       </c>
-      <c r="BC10" s="4" t="inlineStr">
+      <c r="BC10" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD10" s="4" t="inlineStr"/>
-      <c r="BE10" s="4" t="inlineStr">
+      <c r="BD10" s="2" t="inlineStr"/>
+      <c r="BE10" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF10" s="4" t="inlineStr">
+      <c r="BF10" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG10" s="4" t="inlineStr">
+      <c r="BG10" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH10" s="4" t="inlineStr"/>
-      <c r="BI10" s="4" t="inlineStr"/>
-      <c r="BJ10" s="4" t="inlineStr"/>
-      <c r="BK10" s="4" t="inlineStr"/>
-      <c r="BL10" s="4" t="inlineStr"/>
+      <c r="BH10" s="2" t="inlineStr"/>
+      <c r="BI10" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ10" s="2" t="inlineStr"/>
+      <c r="BK10" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -2565,13 +2629,17 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L11" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
@@ -2620,7 +2688,11 @@
         </is>
       </c>
       <c r="AA11" s="4" t="inlineStr"/>
-      <c r="AB11" s="4" t="inlineStr"/>
+      <c r="AB11" s="4" t="inlineStr">
+        <is>
+          <t>cdf7e010b36d430bbf37f508c8d33593</t>
+        </is>
+      </c>
       <c r="AC11" s="4" t="inlineStr">
         <is>
           <t>924cb1e580ddf666427b4bfe</t>
@@ -2641,7 +2713,11 @@
       <c r="AL11" s="4" t="inlineStr"/>
       <c r="AM11" s="4" t="inlineStr"/>
       <c r="AN11" s="4" t="inlineStr"/>
-      <c r="AO11" s="4" t="inlineStr"/>
+      <c r="AO11" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP11" s="4" t="inlineStr"/>
       <c r="AQ11" s="4" t="inlineStr"/>
       <c r="AR11" s="4" t="inlineStr"/>
@@ -2679,356 +2755,412 @@
       <c r="BH11" s="4" t="inlineStr"/>
       <c r="BI11" s="4" t="inlineStr"/>
       <c r="BJ11" s="4" t="inlineStr"/>
-      <c r="BK11" s="4" t="inlineStr"/>
-      <c r="BL11" s="4" t="inlineStr"/>
+      <c r="BK11" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL11" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>IBM</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>International Business Machines Corporation Common Stock</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>2026-09-08T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>IBM Executive: AI Creates Value, Not Job Cuts</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr"/>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L12" s="4" t="inlineStr"/>
-      <c r="M12" s="4" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>'-0.029</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxNY3JtRmZZR3psaEZ1UE03STI0TzJGd2pfeWxSU1BoMmZvZ2JSZUZXcEpMcXhhYUstZ0htRnVia3JOQnZuekxwbVVUOXo2Z0VqM2JjeFFkbWtOSXgxOXdKbGpOUkRheHJxa3VDeUtmajZYV0dTYW43aWhuZ3lwWEhsbGY3a05yRFhk?oc=5</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>조선일보</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr"/>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>job cuts</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>901dcb3675b84715a0d040d92df7abdf</t>
+        </is>
+      </c>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>1f461bbf720d4b72ac19c318</t>
+        </is>
+      </c>
+      <c r="AD12" s="2" t="inlineStr">
+        <is>
+          <t>11da16c62ea71b43e5078a0f</t>
+        </is>
+      </c>
+      <c r="AE12" s="2" t="inlineStr"/>
+      <c r="AF12" s="2" t="inlineStr"/>
+      <c r="AG12" s="2" t="inlineStr"/>
+      <c r="AH12" s="2" t="inlineStr"/>
+      <c r="AI12" s="2" t="inlineStr"/>
+      <c r="AJ12" s="2" t="inlineStr"/>
+      <c r="AK12" s="2" t="inlineStr"/>
+      <c r="AL12" s="2" t="inlineStr"/>
+      <c r="AM12" s="2" t="inlineStr"/>
+      <c r="AN12" s="2" t="inlineStr"/>
+      <c r="AO12" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N12" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O12" s="4" t="inlineStr">
-        <is>
-          <t>'-0.029</t>
-        </is>
-      </c>
-      <c r="P12" s="4" t="inlineStr"/>
-      <c r="Q12" s="4" t="inlineStr"/>
-      <c r="R12" s="4" t="inlineStr"/>
-      <c r="S12" s="4" t="inlineStr"/>
-      <c r="T12" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U12" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxNY3JtRmZZR3psaEZ1UE03STI0TzJGd2pfeWxSU1BoMmZvZ2JSZUZXcEpMcXhhYUstZ0htRnVia3JOQnZuekxwbVVUOXo2Z0VqM2JjeFFkbWtOSXgxOXdKbGpOUkRheHJxa3VDeUtmajZYV0dTYW43aWhuZ3lwWEhsbGY3a05yRFhk?oc=5</t>
-        </is>
-      </c>
-      <c r="V12" s="4" t="inlineStr">
-        <is>
-          <t>조선일보</t>
-        </is>
-      </c>
-      <c r="W12" s="4" t="inlineStr"/>
-      <c r="X12" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y12" s="4" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z12" s="4" t="inlineStr">
-        <is>
-          <t>job cuts</t>
-        </is>
-      </c>
-      <c r="AA12" s="4" t="inlineStr"/>
-      <c r="AB12" s="4" t="inlineStr"/>
-      <c r="AC12" s="4" t="inlineStr">
-        <is>
-          <t>1f461bbf720d4b72ac19c318</t>
-        </is>
-      </c>
-      <c r="AD12" s="4" t="inlineStr">
-        <is>
-          <t>11da16c62ea71b43e5078a0f</t>
-        </is>
-      </c>
-      <c r="AE12" s="4" t="inlineStr"/>
-      <c r="AF12" s="4" t="inlineStr"/>
-      <c r="AG12" s="4" t="inlineStr"/>
-      <c r="AH12" s="4" t="inlineStr"/>
-      <c r="AI12" s="4" t="inlineStr"/>
-      <c r="AJ12" s="4" t="inlineStr"/>
-      <c r="AK12" s="4" t="inlineStr"/>
-      <c r="AL12" s="4" t="inlineStr"/>
-      <c r="AM12" s="4" t="inlineStr"/>
-      <c r="AN12" s="4" t="inlineStr"/>
-      <c r="AO12" s="4" t="inlineStr"/>
-      <c r="AP12" s="4" t="inlineStr"/>
-      <c r="AQ12" s="4" t="inlineStr"/>
-      <c r="AR12" s="4" t="inlineStr"/>
-      <c r="AS12" s="4" t="inlineStr"/>
-      <c r="AT12" s="4" t="inlineStr"/>
-      <c r="AU12" s="4" t="inlineStr"/>
-      <c r="AV12" s="4" t="inlineStr"/>
-      <c r="AW12" s="4" t="inlineStr">
+      <c r="AP12" s="2" t="inlineStr"/>
+      <c r="AQ12" s="2" t="inlineStr"/>
+      <c r="AR12" s="2" t="inlineStr"/>
+      <c r="AS12" s="2" t="inlineStr"/>
+      <c r="AT12" s="2" t="inlineStr"/>
+      <c r="AU12" s="2" t="inlineStr"/>
+      <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" s="2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX12" s="4" t="inlineStr"/>
-      <c r="AY12" s="4" t="inlineStr"/>
-      <c r="AZ12" s="4" t="inlineStr"/>
-      <c r="BA12" s="4" t="inlineStr"/>
-      <c r="BB12" s="4" t="inlineStr">
+      <c r="AX12" s="2" t="inlineStr"/>
+      <c r="AY12" s="2" t="inlineStr"/>
+      <c r="AZ12" s="2" t="inlineStr"/>
+      <c r="BA12" s="2" t="inlineStr"/>
+      <c r="BB12" s="2" t="inlineStr">
         <is>
           <t>IBM</t>
         </is>
       </c>
-      <c r="BC12" s="4" t="inlineStr">
+      <c r="BC12" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD12" s="4" t="inlineStr"/>
-      <c r="BE12" s="4" t="inlineStr">
+      <c r="BD12" s="2" t="inlineStr"/>
+      <c r="BE12" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF12" s="4" t="inlineStr">
+      <c r="BF12" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG12" s="4" t="inlineStr">
+      <c r="BG12" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH12" s="4" t="inlineStr"/>
-      <c r="BI12" s="4" t="inlineStr"/>
-      <c r="BJ12" s="4" t="inlineStr"/>
-      <c r="BK12" s="4" t="inlineStr"/>
-      <c r="BL12" s="4" t="inlineStr"/>
+      <c r="BH12" s="2" t="inlineStr"/>
+      <c r="BI12" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ12" s="2" t="inlineStr"/>
+      <c r="BK12" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>MOS</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Mosaic Company (The) Common Stock</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>2026-09-08T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Partnerships Key to Strengthening Defence Supply Chain Resilience: MOS Desmond Choo at the 15th Seoul Defense Dialogue</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr"/>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>供應鏈中斷</t>
-        </is>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K13" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L13" s="4" t="inlineStr"/>
-      <c r="M13" s="4" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0.762</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTFA4NWJqRGFkbFd2VHBGWlItWWJPdVRNODdaYV9Bd3pWaHpMN29TaGtZTjN6dXR6ay15cjl5ZEFmam9VbFdCS2pPR2tsYV91OUUxU21zRER0V0xaOVpVZmhGVXdsZ2ttT0FheE5MWDRicTAwZ1ZRZWRiTQ?oc=5</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>MINDEF Singapore</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr"/>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>supply chain</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr"/>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>a1bf974974954dedbcb69e4b28ace86d</t>
+        </is>
+      </c>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>9616dd333eb342415ab91203</t>
+        </is>
+      </c>
+      <c r="AD13" s="2" t="inlineStr">
+        <is>
+          <t>32167af3504e704c5911f7dd</t>
+        </is>
+      </c>
+      <c r="AE13" s="2" t="inlineStr"/>
+      <c r="AF13" s="2" t="inlineStr"/>
+      <c r="AG13" s="2" t="inlineStr"/>
+      <c r="AH13" s="2" t="inlineStr"/>
+      <c r="AI13" s="2" t="inlineStr"/>
+      <c r="AJ13" s="2" t="inlineStr"/>
+      <c r="AK13" s="2" t="inlineStr"/>
+      <c r="AL13" s="2" t="inlineStr"/>
+      <c r="AM13" s="2" t="inlineStr"/>
+      <c r="AN13" s="2" t="inlineStr"/>
+      <c r="AO13" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N13" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O13" s="4" t="inlineStr">
-        <is>
-          <t>0.762</t>
-        </is>
-      </c>
-      <c r="P13" s="4" t="inlineStr"/>
-      <c r="Q13" s="4" t="inlineStr"/>
-      <c r="R13" s="4" t="inlineStr"/>
-      <c r="S13" s="4" t="inlineStr"/>
-      <c r="T13" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U13" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTFA4NWJqRGFkbFd2VHBGWlItWWJPdVRNODdaYV9Bd3pWaHpMN29TaGtZTjN6dXR6ay15cjl5ZEFmam9VbFdCS2pPR2tsYV91OUUxU21zRER0V0xaOVpVZmhGVXdsZ2ttT0FheE5MWDRicTAwZ1ZRZWRiTQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V13" s="4" t="inlineStr">
-        <is>
-          <t>MINDEF Singapore</t>
-        </is>
-      </c>
-      <c r="W13" s="4" t="inlineStr"/>
-      <c r="X13" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y13" s="4" t="inlineStr">
-        <is>
-          <t>SUPPLY_CHAIN_DISRUPTION</t>
-        </is>
-      </c>
-      <c r="Z13" s="4" t="inlineStr">
-        <is>
-          <t>supply chain</t>
-        </is>
-      </c>
-      <c r="AA13" s="4" t="inlineStr"/>
-      <c r="AB13" s="4" t="inlineStr"/>
-      <c r="AC13" s="4" t="inlineStr">
-        <is>
-          <t>9616dd333eb342415ab91203</t>
-        </is>
-      </c>
-      <c r="AD13" s="4" t="inlineStr">
-        <is>
-          <t>32167af3504e704c5911f7dd</t>
-        </is>
-      </c>
-      <c r="AE13" s="4" t="inlineStr"/>
-      <c r="AF13" s="4" t="inlineStr"/>
-      <c r="AG13" s="4" t="inlineStr"/>
-      <c r="AH13" s="4" t="inlineStr"/>
-      <c r="AI13" s="4" t="inlineStr"/>
-      <c r="AJ13" s="4" t="inlineStr"/>
-      <c r="AK13" s="4" t="inlineStr"/>
-      <c r="AL13" s="4" t="inlineStr"/>
-      <c r="AM13" s="4" t="inlineStr"/>
-      <c r="AN13" s="4" t="inlineStr"/>
-      <c r="AO13" s="4" t="inlineStr"/>
-      <c r="AP13" s="4" t="inlineStr"/>
-      <c r="AQ13" s="4" t="inlineStr"/>
-      <c r="AR13" s="4" t="inlineStr"/>
-      <c r="AS13" s="4" t="inlineStr"/>
-      <c r="AT13" s="4" t="inlineStr"/>
-      <c r="AU13" s="4" t="inlineStr"/>
-      <c r="AV13" s="4" t="inlineStr"/>
-      <c r="AW13" s="4" t="inlineStr">
+      <c r="AP13" s="2" t="inlineStr"/>
+      <c r="AQ13" s="2" t="inlineStr"/>
+      <c r="AR13" s="2" t="inlineStr"/>
+      <c r="AS13" s="2" t="inlineStr"/>
+      <c r="AT13" s="2" t="inlineStr"/>
+      <c r="AU13" s="2" t="inlineStr"/>
+      <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" s="2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX13" s="4" t="inlineStr"/>
-      <c r="AY13" s="4" t="inlineStr"/>
-      <c r="AZ13" s="4" t="inlineStr"/>
-      <c r="BA13" s="4" t="inlineStr"/>
-      <c r="BB13" s="4" t="inlineStr">
+      <c r="AX13" s="2" t="inlineStr"/>
+      <c r="AY13" s="2" t="inlineStr"/>
+      <c r="AZ13" s="2" t="inlineStr"/>
+      <c r="BA13" s="2" t="inlineStr"/>
+      <c r="BB13" s="2" t="inlineStr">
         <is>
           <t>MOS</t>
         </is>
       </c>
-      <c r="BC13" s="4" t="inlineStr">
+      <c r="BC13" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD13" s="4" t="inlineStr"/>
-      <c r="BE13" s="4" t="inlineStr">
+      <c r="BD13" s="2" t="inlineStr"/>
+      <c r="BE13" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF13" s="4" t="inlineStr">
+      <c r="BF13" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG13" s="4" t="inlineStr">
+      <c r="BG13" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH13" s="4" t="inlineStr"/>
-      <c r="BI13" s="4" t="inlineStr"/>
-      <c r="BJ13" s="4" t="inlineStr"/>
-      <c r="BK13" s="4" t="inlineStr"/>
-      <c r="BL13" s="4" t="inlineStr"/>
+      <c r="BH13" s="2" t="inlineStr"/>
+      <c r="BI13" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ13" s="2" t="inlineStr"/>
+      <c r="BK13" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -4592,7 +4724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL9"/>
+  <dimension ref="A1:BL6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5420,13 +5552,17 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M4" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N4" s="4" t="inlineStr">
@@ -5475,7 +5611,11 @@
         </is>
       </c>
       <c r="AA4" s="4" t="inlineStr"/>
-      <c r="AB4" s="4" t="inlineStr"/>
+      <c r="AB4" s="4" t="inlineStr">
+        <is>
+          <t>6e48a6637e46437b9a5183851b9eb389</t>
+        </is>
+      </c>
       <c r="AC4" s="4" t="inlineStr">
         <is>
           <t>b8c1e2d4bf121f76b50f7cbb</t>
@@ -5496,7 +5636,11 @@
       <c r="AL4" s="4" t="inlineStr"/>
       <c r="AM4" s="4" t="inlineStr"/>
       <c r="AN4" s="4" t="inlineStr"/>
-      <c r="AO4" s="4" t="inlineStr"/>
+      <c r="AO4" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP4" s="4" t="inlineStr"/>
       <c r="AQ4" s="4" t="inlineStr"/>
       <c r="AR4" s="4" t="inlineStr"/>
@@ -5542,8 +5686,16 @@
       <c r="BH4" s="4" t="inlineStr"/>
       <c r="BI4" s="4" t="inlineStr"/>
       <c r="BJ4" s="4" t="inlineStr"/>
-      <c r="BK4" s="4" t="inlineStr"/>
-      <c r="BL4" s="4" t="inlineStr"/>
+      <c r="BK4" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL4" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -5594,13 +5746,17 @@
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr">
@@ -5649,7 +5805,11 @@
         </is>
       </c>
       <c r="AA5" s="4" t="inlineStr"/>
-      <c r="AB5" s="4" t="inlineStr"/>
+      <c r="AB5" s="4" t="inlineStr">
+        <is>
+          <t>8de77b64f76b44bc9118522a8f683454</t>
+        </is>
+      </c>
       <c r="AC5" s="4" t="inlineStr">
         <is>
           <t>92feddbb567496d7c9a51001</t>
@@ -5670,7 +5830,11 @@
       <c r="AL5" s="4" t="inlineStr"/>
       <c r="AM5" s="4" t="inlineStr"/>
       <c r="AN5" s="4" t="inlineStr"/>
-      <c r="AO5" s="4" t="inlineStr"/>
+      <c r="AO5" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP5" s="4" t="inlineStr"/>
       <c r="AQ5" s="4" t="inlineStr"/>
       <c r="AR5" s="4" t="inlineStr"/>
@@ -5716,8 +5880,16 @@
       <c r="BH5" s="4" t="inlineStr"/>
       <c r="BI5" s="4" t="inlineStr"/>
       <c r="BJ5" s="4" t="inlineStr"/>
-      <c r="BK5" s="4" t="inlineStr"/>
-      <c r="BL5" s="4" t="inlineStr"/>
+      <c r="BK5" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL5" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -5732,12 +5904,12 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Uber Technologies, Inc. Common Stock</t>
+          <t>PayPal</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -5747,7 +5919,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Top Uber Executive Buys $5.3 Million in Stock After Job Cuts</t>
+          <t>With PayPal Layoffs Brewing, How to Play PYPL Stock in September 2026</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr"/>
@@ -5768,13 +5940,17 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L6" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N6" s="4" t="inlineStr">
@@ -5784,7 +5960,7 @@
       </c>
       <c r="O6" s="4" t="inlineStr">
         <is>
-          <t>'-0.136</t>
+          <t>'-0.056</t>
         </is>
       </c>
       <c r="P6" s="4" t="inlineStr"/>
@@ -5798,12 +5974,12 @@
       </c>
       <c r="U6" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE41dlAzbGVaQzNqaEpuZ1hTbjFjVXltczFmWmVkLTV3RFEycGtDbm42TDFLeVNnM2ZqakJKOTlnS01qZGFxQUk2dThFRkhqVzJjYVEyZHlYS3A2UFJSRjRXTkgxM3hMQkFIM09Gb09TOEhGOTJYSnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNbmdTWnN1VDFxbUdhc2wzLTloNGgtTkwzMEw5Sm4wT3dhZ0Zza1hkaXVHTmR3RVdWYUhtaG9pdWdiMzI0OHh1YUxnbTZldlBrT3h2NnNFaGlGczlFUi1KdEJQVFFSRTN3Sk9EczlMaTFhMU95RWRyUzNvNHlqVjFPeWc4SW5oYVJqYmlUMzMxMkdUYmFwdk1TRHQ2VktlNlZhNFpkVnZuY0FPT2NscE9ZZVJR?oc=5</t>
         </is>
       </c>
       <c r="V6" s="4" t="inlineStr">
         <is>
-          <t>Barron's</t>
+          <t>Barchart.com</t>
         </is>
       </c>
       <c r="W6" s="4" t="inlineStr"/>
@@ -5819,19 +5995,23 @@
       </c>
       <c r="Z6" s="4" t="inlineStr">
         <is>
-          <t>job cuts</t>
+          <t>layoff；layoffs</t>
         </is>
       </c>
       <c r="AA6" s="4" t="inlineStr"/>
-      <c r="AB6" s="4" t="inlineStr"/>
+      <c r="AB6" s="4" t="inlineStr">
+        <is>
+          <t>cdf7e010b36d430bbf37f508c8d33593</t>
+        </is>
+      </c>
       <c r="AC6" s="4" t="inlineStr">
         <is>
-          <t>afe86c8885c0ca93d5aeb3f5</t>
+          <t>924cb1e580ddf666427b4bfe</t>
         </is>
       </c>
       <c r="AD6" s="4" t="inlineStr">
         <is>
-          <t>e5b42f025d14a0b387654dbc</t>
+          <t>d2ff43426fda5fe85b0b80dd</t>
         </is>
       </c>
       <c r="AE6" s="4" t="inlineStr"/>
@@ -5844,7 +6024,11 @@
       <c r="AL6" s="4" t="inlineStr"/>
       <c r="AM6" s="4" t="inlineStr"/>
       <c r="AN6" s="4" t="inlineStr"/>
-      <c r="AO6" s="4" t="inlineStr"/>
+      <c r="AO6" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP6" s="4" t="inlineStr"/>
       <c r="AQ6" s="4" t="inlineStr"/>
       <c r="AR6" s="4" t="inlineStr"/>
@@ -5852,18 +6036,14 @@
       <c r="AT6" s="4" t="inlineStr"/>
       <c r="AU6" s="4" t="inlineStr"/>
       <c r="AV6" s="4" t="inlineStr"/>
-      <c r="AW6" s="4" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
+      <c r="AW6" s="4" t="inlineStr"/>
       <c r="AX6" s="4" t="inlineStr"/>
       <c r="AY6" s="4" t="inlineStr"/>
       <c r="AZ6" s="4" t="inlineStr"/>
       <c r="BA6" s="4" t="inlineStr"/>
       <c r="BB6" s="4" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="BC6" s="4" t="inlineStr">
@@ -5874,541 +6054,31 @@
       <c r="BD6" s="4" t="inlineStr"/>
       <c r="BE6" s="4" t="inlineStr">
         <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF6" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
+          <t>公司清單</t>
+        </is>
+      </c>
+      <c r="BF6" s="4" t="inlineStr"/>
       <c r="BG6" s="4" t="inlineStr">
         <is>
-          <t>交易所目前名單</t>
+          <t>公司清單／交易所參照</t>
         </is>
       </c>
       <c r="BH6" s="4" t="inlineStr"/>
       <c r="BI6" s="4" t="inlineStr"/>
       <c r="BJ6" s="4" t="inlineStr"/>
-      <c r="BK6" s="4" t="inlineStr"/>
-      <c r="BL6" s="4" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>PYPL</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>PayPal</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-08T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>With PayPal Layoffs Brewing, How to Play PYPL Stock in September 2026</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr"/>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K7" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L7" s="4" t="inlineStr"/>
-      <c r="M7" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N7" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O7" s="4" t="inlineStr">
-        <is>
-          <t>'-0.056</t>
-        </is>
-      </c>
-      <c r="P7" s="4" t="inlineStr"/>
-      <c r="Q7" s="4" t="inlineStr"/>
-      <c r="R7" s="4" t="inlineStr"/>
-      <c r="S7" s="4" t="inlineStr"/>
-      <c r="T7" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U7" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNbmdTWnN1VDFxbUdhc2wzLTloNGgtTkwzMEw5Sm4wT3dhZ0Zza1hkaXVHTmR3RVdWYUhtaG9pdWdiMzI0OHh1YUxnbTZldlBrT3h2NnNFaGlGczlFUi1KdEJQVFFSRTN3Sk9EczlMaTFhMU95RWRyUzNvNHlqVjFPeWc4SW5oYVJqYmlUMzMxMkdUYmFwdk1TRHQ2VktlNlZhNFpkVnZuY0FPT2NscE9ZZVJR?oc=5</t>
-        </is>
-      </c>
-      <c r="V7" s="4" t="inlineStr">
-        <is>
-          <t>Barchart.com</t>
-        </is>
-      </c>
-      <c r="W7" s="4" t="inlineStr"/>
-      <c r="X7" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y7" s="4" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z7" s="4" t="inlineStr">
-        <is>
-          <t>layoff；layoffs</t>
-        </is>
-      </c>
-      <c r="AA7" s="4" t="inlineStr"/>
-      <c r="AB7" s="4" t="inlineStr"/>
-      <c r="AC7" s="4" t="inlineStr">
-        <is>
-          <t>924cb1e580ddf666427b4bfe</t>
-        </is>
-      </c>
-      <c r="AD7" s="4" t="inlineStr">
-        <is>
-          <t>d2ff43426fda5fe85b0b80dd</t>
-        </is>
-      </c>
-      <c r="AE7" s="4" t="inlineStr"/>
-      <c r="AF7" s="4" t="inlineStr"/>
-      <c r="AG7" s="4" t="inlineStr"/>
-      <c r="AH7" s="4" t="inlineStr"/>
-      <c r="AI7" s="4" t="inlineStr"/>
-      <c r="AJ7" s="4" t="inlineStr"/>
-      <c r="AK7" s="4" t="inlineStr"/>
-      <c r="AL7" s="4" t="inlineStr"/>
-      <c r="AM7" s="4" t="inlineStr"/>
-      <c r="AN7" s="4" t="inlineStr"/>
-      <c r="AO7" s="4" t="inlineStr"/>
-      <c r="AP7" s="4" t="inlineStr"/>
-      <c r="AQ7" s="4" t="inlineStr"/>
-      <c r="AR7" s="4" t="inlineStr"/>
-      <c r="AS7" s="4" t="inlineStr"/>
-      <c r="AT7" s="4" t="inlineStr"/>
-      <c r="AU7" s="4" t="inlineStr"/>
-      <c r="AV7" s="4" t="inlineStr"/>
-      <c r="AW7" s="4" t="inlineStr"/>
-      <c r="AX7" s="4" t="inlineStr"/>
-      <c r="AY7" s="4" t="inlineStr"/>
-      <c r="AZ7" s="4" t="inlineStr"/>
-      <c r="BA7" s="4" t="inlineStr"/>
-      <c r="BB7" s="4" t="inlineStr">
-        <is>
-          <t>PYPL</t>
-        </is>
-      </c>
-      <c r="BC7" s="4" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD7" s="4" t="inlineStr"/>
-      <c r="BE7" s="4" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF7" s="4" t="inlineStr"/>
-      <c r="BG7" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH7" s="4" t="inlineStr"/>
-      <c r="BI7" s="4" t="inlineStr"/>
-      <c r="BJ7" s="4" t="inlineStr"/>
-      <c r="BK7" s="4" t="inlineStr"/>
-      <c r="BL7" s="4" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>IBM</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>International Business Machines Corporation Common Stock</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-08T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>IBM Executive: AI Creates Value, Not Job Cuts</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr"/>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K8" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L8" s="4" t="inlineStr"/>
-      <c r="M8" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N8" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O8" s="4" t="inlineStr">
-        <is>
-          <t>'-0.029</t>
-        </is>
-      </c>
-      <c r="P8" s="4" t="inlineStr"/>
-      <c r="Q8" s="4" t="inlineStr"/>
-      <c r="R8" s="4" t="inlineStr"/>
-      <c r="S8" s="4" t="inlineStr"/>
-      <c r="T8" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U8" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxNY3JtRmZZR3psaEZ1UE03STI0TzJGd2pfeWxSU1BoMmZvZ2JSZUZXcEpMcXhhYUstZ0htRnVia3JOQnZuekxwbVVUOXo2Z0VqM2JjeFFkbWtOSXgxOXdKbGpOUkRheHJxa3VDeUtmajZYV0dTYW43aWhuZ3lwWEhsbGY3a05yRFhk?oc=5</t>
-        </is>
-      </c>
-      <c r="V8" s="4" t="inlineStr">
-        <is>
-          <t>조선일보</t>
-        </is>
-      </c>
-      <c r="W8" s="4" t="inlineStr"/>
-      <c r="X8" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y8" s="4" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z8" s="4" t="inlineStr">
-        <is>
-          <t>job cuts</t>
-        </is>
-      </c>
-      <c r="AA8" s="4" t="inlineStr"/>
-      <c r="AB8" s="4" t="inlineStr"/>
-      <c r="AC8" s="4" t="inlineStr">
-        <is>
-          <t>1f461bbf720d4b72ac19c318</t>
-        </is>
-      </c>
-      <c r="AD8" s="4" t="inlineStr">
-        <is>
-          <t>11da16c62ea71b43e5078a0f</t>
-        </is>
-      </c>
-      <c r="AE8" s="4" t="inlineStr"/>
-      <c r="AF8" s="4" t="inlineStr"/>
-      <c r="AG8" s="4" t="inlineStr"/>
-      <c r="AH8" s="4" t="inlineStr"/>
-      <c r="AI8" s="4" t="inlineStr"/>
-      <c r="AJ8" s="4" t="inlineStr"/>
-      <c r="AK8" s="4" t="inlineStr"/>
-      <c r="AL8" s="4" t="inlineStr"/>
-      <c r="AM8" s="4" t="inlineStr"/>
-      <c r="AN8" s="4" t="inlineStr"/>
-      <c r="AO8" s="4" t="inlineStr"/>
-      <c r="AP8" s="4" t="inlineStr"/>
-      <c r="AQ8" s="4" t="inlineStr"/>
-      <c r="AR8" s="4" t="inlineStr"/>
-      <c r="AS8" s="4" t="inlineStr"/>
-      <c r="AT8" s="4" t="inlineStr"/>
-      <c r="AU8" s="4" t="inlineStr"/>
-      <c r="AV8" s="4" t="inlineStr"/>
-      <c r="AW8" s="4" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX8" s="4" t="inlineStr"/>
-      <c r="AY8" s="4" t="inlineStr"/>
-      <c r="AZ8" s="4" t="inlineStr"/>
-      <c r="BA8" s="4" t="inlineStr"/>
-      <c r="BB8" s="4" t="inlineStr">
-        <is>
-          <t>IBM</t>
-        </is>
-      </c>
-      <c r="BC8" s="4" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD8" s="4" t="inlineStr"/>
-      <c r="BE8" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF8" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG8" s="4" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH8" s="4" t="inlineStr"/>
-      <c r="BI8" s="4" t="inlineStr"/>
-      <c r="BJ8" s="4" t="inlineStr"/>
-      <c r="BK8" s="4" t="inlineStr"/>
-      <c r="BL8" s="4" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>MOS</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>Mosaic Company (The) Common Stock</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-08T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>Partnerships Key to Strengthening Defence Supply Chain Resilience: MOS Desmond Choo at the 15th Seoul Defense Dialogue</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr"/>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>供應鏈中斷</t>
-        </is>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K9" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L9" s="4" t="inlineStr"/>
-      <c r="M9" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N9" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O9" s="4" t="inlineStr">
-        <is>
-          <t>0.762</t>
-        </is>
-      </c>
-      <c r="P9" s="4" t="inlineStr"/>
-      <c r="Q9" s="4" t="inlineStr"/>
-      <c r="R9" s="4" t="inlineStr"/>
-      <c r="S9" s="4" t="inlineStr"/>
-      <c r="T9" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U9" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTFA4NWJqRGFkbFd2VHBGWlItWWJPdVRNODdaYV9Bd3pWaHpMN29TaGtZTjN6dXR6ay15cjl5ZEFmam9VbFdCS2pPR2tsYV91OUUxU21zRER0V0xaOVpVZmhGVXdsZ2ttT0FheE5MWDRicTAwZ1ZRZWRiTQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V9" s="4" t="inlineStr">
-        <is>
-          <t>MINDEF Singapore</t>
-        </is>
-      </c>
-      <c r="W9" s="4" t="inlineStr"/>
-      <c r="X9" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y9" s="4" t="inlineStr">
-        <is>
-          <t>SUPPLY_CHAIN_DISRUPTION</t>
-        </is>
-      </c>
-      <c r="Z9" s="4" t="inlineStr">
-        <is>
-          <t>supply chain</t>
-        </is>
-      </c>
-      <c r="AA9" s="4" t="inlineStr"/>
-      <c r="AB9" s="4" t="inlineStr"/>
-      <c r="AC9" s="4" t="inlineStr">
-        <is>
-          <t>9616dd333eb342415ab91203</t>
-        </is>
-      </c>
-      <c r="AD9" s="4" t="inlineStr">
-        <is>
-          <t>32167af3504e704c5911f7dd</t>
-        </is>
-      </c>
-      <c r="AE9" s="4" t="inlineStr"/>
-      <c r="AF9" s="4" t="inlineStr"/>
-      <c r="AG9" s="4" t="inlineStr"/>
-      <c r="AH9" s="4" t="inlineStr"/>
-      <c r="AI9" s="4" t="inlineStr"/>
-      <c r="AJ9" s="4" t="inlineStr"/>
-      <c r="AK9" s="4" t="inlineStr"/>
-      <c r="AL9" s="4" t="inlineStr"/>
-      <c r="AM9" s="4" t="inlineStr"/>
-      <c r="AN9" s="4" t="inlineStr"/>
-      <c r="AO9" s="4" t="inlineStr"/>
-      <c r="AP9" s="4" t="inlineStr"/>
-      <c r="AQ9" s="4" t="inlineStr"/>
-      <c r="AR9" s="4" t="inlineStr"/>
-      <c r="AS9" s="4" t="inlineStr"/>
-      <c r="AT9" s="4" t="inlineStr"/>
-      <c r="AU9" s="4" t="inlineStr"/>
-      <c r="AV9" s="4" t="inlineStr"/>
-      <c r="AW9" s="4" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX9" s="4" t="inlineStr"/>
-      <c r="AY9" s="4" t="inlineStr"/>
-      <c r="AZ9" s="4" t="inlineStr"/>
-      <c r="BA9" s="4" t="inlineStr"/>
-      <c r="BB9" s="4" t="inlineStr">
-        <is>
-          <t>MOS</t>
-        </is>
-      </c>
-      <c r="BC9" s="4" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD9" s="4" t="inlineStr"/>
-      <c r="BE9" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF9" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG9" s="4" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH9" s="4" t="inlineStr"/>
-      <c r="BI9" s="4" t="inlineStr"/>
-      <c r="BJ9" s="4" t="inlineStr"/>
-      <c r="BK9" s="4" t="inlineStr"/>
-      <c r="BL9" s="4" t="inlineStr"/>
+      <c r="BK6" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL6" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BL9"/>
+  <autoFilter ref="A1:BL6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/news_daily/2026-09-08.xlsx
+++ b/news_daily/2026-09-08.xlsx
@@ -1093,13 +1093,17 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -1148,7 +1152,11 @@
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr"/>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>f9c1779442454a3ab98a345ae828036b</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
           <t>c21718b1c0dcb59110dc7a07</t>
@@ -1169,7 +1177,11 @@
       <c r="AL3" s="2" t="inlineStr"/>
       <c r="AM3" s="2" t="inlineStr"/>
       <c r="AN3" s="2" t="inlineStr"/>
-      <c r="AO3" s="2" t="inlineStr"/>
+      <c r="AO3" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP3" s="2" t="inlineStr"/>
       <c r="AQ3" s="2" t="inlineStr"/>
       <c r="AR3" s="2" t="inlineStr"/>
@@ -1215,8 +1227,16 @@
       <c r="BH3" s="2" t="inlineStr"/>
       <c r="BI3" s="2" t="inlineStr"/>
       <c r="BJ3" s="2" t="inlineStr"/>
-      <c r="BK3" s="2" t="inlineStr"/>
-      <c r="BL3" s="2" t="inlineStr"/>
+      <c r="BK3" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -3211,13 +3231,17 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3266,7 +3290,11 @@
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr"/>
-      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>5c26c53d34cf453aac7df0926b4a8b7c</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
           <t>2fd7737902651b53746111c6</t>
@@ -3287,7 +3315,11 @@
       <c r="AL14" s="2" t="inlineStr"/>
       <c r="AM14" s="2" t="inlineStr"/>
       <c r="AN14" s="2" t="inlineStr"/>
-      <c r="AO14" s="2" t="inlineStr"/>
+      <c r="AO14" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP14" s="2" t="inlineStr"/>
       <c r="AQ14" s="2" t="inlineStr"/>
       <c r="AR14" s="2" t="inlineStr"/>
@@ -3333,8 +3365,16 @@
       <c r="BH14" s="2" t="inlineStr"/>
       <c r="BI14" s="2" t="inlineStr"/>
       <c r="BJ14" s="2" t="inlineStr"/>
-      <c r="BK14" s="2" t="inlineStr"/>
-      <c r="BL14" s="2" t="inlineStr"/>
+      <c r="BK14" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3370,28 +3410,32 @@
       <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>關稅</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3431,7 +3475,7 @@
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>TARIFF</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
@@ -3440,7 +3484,11 @@
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr"/>
-      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>bdfff595e4c34f0089fb9baac39cf030</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
           <t>03072db1a3750321c256aa76</t>
@@ -3461,7 +3509,11 @@
       <c r="AL15" s="2" t="inlineStr"/>
       <c r="AM15" s="2" t="inlineStr"/>
       <c r="AN15" s="2" t="inlineStr"/>
-      <c r="AO15" s="2" t="inlineStr"/>
+      <c r="AO15" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP15" s="2" t="inlineStr"/>
       <c r="AQ15" s="2" t="inlineStr"/>
       <c r="AR15" s="2" t="inlineStr"/>
@@ -3505,10 +3557,22 @@
         </is>
       </c>
       <c r="BH15" s="2" t="inlineStr"/>
-      <c r="BI15" s="2" t="inlineStr"/>
+      <c r="BI15" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ15" s="2" t="inlineStr"/>
-      <c r="BK15" s="2" t="inlineStr"/>
-      <c r="BL15" s="2" t="inlineStr"/>
+      <c r="BK15" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3544,28 +3608,32 @@
       <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>分析師降評</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -3605,7 +3673,7 @@
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>ANALYST_DOWNGRADE</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
@@ -3614,7 +3682,11 @@
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr"/>
-      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>5a3a6687bcf944ab92c8ea37082ec04d</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
           <t>a4ff1c2a80c8151c4797c43a</t>
@@ -3635,7 +3707,11 @@
       <c r="AL16" s="2" t="inlineStr"/>
       <c r="AM16" s="2" t="inlineStr"/>
       <c r="AN16" s="2" t="inlineStr"/>
-      <c r="AO16" s="2" t="inlineStr"/>
+      <c r="AO16" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP16" s="2" t="inlineStr"/>
       <c r="AQ16" s="2" t="inlineStr"/>
       <c r="AR16" s="2" t="inlineStr"/>
@@ -3679,10 +3755,22 @@
         </is>
       </c>
       <c r="BH16" s="2" t="inlineStr"/>
-      <c r="BI16" s="2" t="inlineStr"/>
+      <c r="BI16" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ16" s="2" t="inlineStr"/>
-      <c r="BK16" s="2" t="inlineStr"/>
-      <c r="BL16" s="2" t="inlineStr"/>
+      <c r="BK16" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3718,28 +3806,32 @@
       <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -3779,7 +3871,7 @@
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
@@ -3788,7 +3880,11 @@
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr"/>
-      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>a09ba5027e4b412c8271db2b047e73a8</t>
+        </is>
+      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
           <t>dca2358d8967d9fcd9ece916</t>
@@ -3809,7 +3905,11 @@
       <c r="AL17" s="2" t="inlineStr"/>
       <c r="AM17" s="2" t="inlineStr"/>
       <c r="AN17" s="2" t="inlineStr"/>
-      <c r="AO17" s="2" t="inlineStr"/>
+      <c r="AO17" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP17" s="2" t="inlineStr"/>
       <c r="AQ17" s="2" t="inlineStr"/>
       <c r="AR17" s="2" t="inlineStr"/>
@@ -3853,10 +3953,22 @@
         </is>
       </c>
       <c r="BH17" s="2" t="inlineStr"/>
-      <c r="BI17" s="2" t="inlineStr"/>
+      <c r="BI17" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ17" s="2" t="inlineStr"/>
-      <c r="BK17" s="2" t="inlineStr"/>
-      <c r="BL17" s="2" t="inlineStr"/>
+      <c r="BK17" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL17" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3892,28 +4004,32 @@
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -3953,7 +4069,7 @@
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
@@ -3962,7 +4078,11 @@
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr"/>
-      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>869a6e493b5c4d80bbf894ee0e2f14fb</t>
+        </is>
+      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
           <t>a14b2ce1a70e53f1bee1ff22</t>
@@ -3983,7 +4103,11 @@
       <c r="AL18" s="2" t="inlineStr"/>
       <c r="AM18" s="2" t="inlineStr"/>
       <c r="AN18" s="2" t="inlineStr"/>
-      <c r="AO18" s="2" t="inlineStr"/>
+      <c r="AO18" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP18" s="2" t="inlineStr"/>
       <c r="AQ18" s="2" t="inlineStr"/>
       <c r="AR18" s="2" t="inlineStr"/>
@@ -4019,10 +4143,22 @@
         </is>
       </c>
       <c r="BH18" s="2" t="inlineStr"/>
-      <c r="BI18" s="2" t="inlineStr"/>
+      <c r="BI18" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ18" s="2" t="inlineStr"/>
-      <c r="BK18" s="2" t="inlineStr"/>
-      <c r="BL18" s="2" t="inlineStr"/>
+      <c r="BK18" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4058,28 +4194,32 @@
       <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4119,7 +4259,7 @@
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
@@ -4128,7 +4268,11 @@
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr"/>
-      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>a8354c813bc541f682cad831e7a261d3</t>
+        </is>
+      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
           <t>b532fc5ce0985281ddf048db</t>
@@ -4149,7 +4293,11 @@
       <c r="AL19" s="2" t="inlineStr"/>
       <c r="AM19" s="2" t="inlineStr"/>
       <c r="AN19" s="2" t="inlineStr"/>
-      <c r="AO19" s="2" t="inlineStr"/>
+      <c r="AO19" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP19" s="2" t="inlineStr"/>
       <c r="AQ19" s="2" t="inlineStr"/>
       <c r="AR19" s="2" t="inlineStr"/>
@@ -4185,10 +4333,22 @@
         </is>
       </c>
       <c r="BH19" s="2" t="inlineStr"/>
-      <c r="BI19" s="2" t="inlineStr"/>
+      <c r="BI19" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ19" s="2" t="inlineStr"/>
-      <c r="BK19" s="2" t="inlineStr"/>
-      <c r="BL19" s="2" t="inlineStr"/>
+      <c r="BK19" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL19" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4224,28 +4384,32 @@
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>關稅</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -4285,7 +4449,7 @@
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>TARIFF</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
@@ -4294,7 +4458,11 @@
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr"/>
-      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>baa9f1b88952478fb54b7bac07859f35</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
           <t>610c55029de59dc5a46b4702</t>
@@ -4315,7 +4483,11 @@
       <c r="AL20" s="2" t="inlineStr"/>
       <c r="AM20" s="2" t="inlineStr"/>
       <c r="AN20" s="2" t="inlineStr"/>
-      <c r="AO20" s="2" t="inlineStr"/>
+      <c r="AO20" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP20" s="2" t="inlineStr"/>
       <c r="AQ20" s="2" t="inlineStr"/>
       <c r="AR20" s="2" t="inlineStr"/>
@@ -4359,10 +4531,22 @@
         </is>
       </c>
       <c r="BH20" s="2" t="inlineStr"/>
-      <c r="BI20" s="2" t="inlineStr"/>
+      <c r="BI20" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ20" s="2" t="inlineStr"/>
-      <c r="BK20" s="2" t="inlineStr"/>
-      <c r="BL20" s="2" t="inlineStr"/>
+      <c r="BK20" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4413,13 +4597,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -4468,7 +4656,11 @@
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr"/>
-      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>644f9b68f119454a94cc650bf60eab49</t>
+        </is>
+      </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
           <t>60ddb96394107cb28d5b4b9d</t>
@@ -4489,7 +4681,11 @@
       <c r="AL21" s="2" t="inlineStr"/>
       <c r="AM21" s="2" t="inlineStr"/>
       <c r="AN21" s="2" t="inlineStr"/>
-      <c r="AO21" s="2" t="inlineStr"/>
+      <c r="AO21" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP21" s="2" t="inlineStr"/>
       <c r="AQ21" s="2" t="inlineStr"/>
       <c r="AR21" s="2" t="inlineStr"/>
@@ -4535,8 +4731,16 @@
       <c r="BH21" s="2" t="inlineStr"/>
       <c r="BI21" s="2" t="inlineStr"/>
       <c r="BJ21" s="2" t="inlineStr"/>
-      <c r="BK21" s="2" t="inlineStr"/>
-      <c r="BL21" s="2" t="inlineStr"/>
+      <c r="BK21" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL21" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4572,28 +4776,32 @@
       <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>分析師降評</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -4633,7 +4841,7 @@
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>ANALYST_DOWNGRADE</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
@@ -4642,7 +4850,11 @@
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr"/>
-      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>800df51c920243d0b4dab8e6b4ca4c88</t>
+        </is>
+      </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
           <t>01a30625f92c34a1e2ec2a92</t>
@@ -4663,7 +4875,11 @@
       <c r="AL22" s="2" t="inlineStr"/>
       <c r="AM22" s="2" t="inlineStr"/>
       <c r="AN22" s="2" t="inlineStr"/>
-      <c r="AO22" s="2" t="inlineStr"/>
+      <c r="AO22" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP22" s="2" t="inlineStr"/>
       <c r="AQ22" s="2" t="inlineStr"/>
       <c r="AR22" s="2" t="inlineStr"/>
@@ -4707,10 +4923,22 @@
         </is>
       </c>
       <c r="BH22" s="2" t="inlineStr"/>
-      <c r="BI22" s="2" t="inlineStr"/>
+      <c r="BI22" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ22" s="2" t="inlineStr"/>
-      <c r="BK22" s="2" t="inlineStr"/>
-      <c r="BL22" s="2" t="inlineStr"/>
+      <c r="BK22" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:BL22"/>
